--- a/data/credit_bond_all_2026-08-31.xlsx
+++ b/data/credit_bond_all_2026-08-31.xlsx
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8700</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -930,7 +930,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>012682176.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>0.27Y</t>
@@ -969,7 +973,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.5000</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1150,7 +1154,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>102683459.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -1189,7 +1197,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6000</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1362,7 +1370,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26晋能电力GN005</t>
+          <t>26晋能电力GN005(碳中和债)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1370,7 +1378,11 @@
           <t>09-01 18:00</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>132680093.IB</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -1590,7 +1602,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>102683460.IB</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -1629,7 +1645,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1814,7 +1830,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>012682179.IB</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>0.49Y</t>
@@ -1853,7 +1873,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5600/1.5300</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -2081,7 +2101,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8300</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -2266,7 +2286,11 @@
           <t>09-01 18:00</t>
         </is>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>102683466.IB</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -2305,7 +2329,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9200/1.8700</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2478,7 +2502,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团GN004</t>
+          <t>26越秀集团MTN004(绿色)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2498,7 +2522,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.94 ~ 2.34</t>
+          <t>1.94 ~ 2.35</t>
         </is>
       </c>
       <c r="H11" s="3"/>
@@ -2525,7 +2549,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/2.3000</t>
+          <t>2.3600/2.3000</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -2702,7 +2726,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y3</t>
+          <t>26高教投资PPN002</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2710,45 +2734,41 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>520450.SZ</t>
-        </is>
-      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.5</v>
+        <v>4.17</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 3.00</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>26高教投资PPN001</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>56D</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2.1185</t>
+          <t>1.6401</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2758,12 +2778,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>泰州高教投资发展有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>C+ 34.77</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2773,7 +2793,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2783,50 +2803,46 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>成都中小企业融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2836,79 +2852,83 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
+          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP12" s="3"/>
-      <c r="AQ12" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -2926,49 +2946,53 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN002</t>
+          <t>26金霞01</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
-        </is>
-      </c>
-      <c r="C13" s="3"/>
+          <t>08-31 17:00</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>283880.SH</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.17</v>
+        <v>6.0</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN001</t>
+          <t>25金霞01</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>56D</t>
+          <t>4.13Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.6401</t>
+          <t>1.9475</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -2978,12 +3002,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司</t>
+          <t>湖南金霞发展集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.77</t>
+          <t>C- 11.49</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2993,7 +3017,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3010,39 +3034,39 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3052,12 +3076,12 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
+          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3067,13 +3091,13 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t/>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
@@ -3088,12 +3112,12 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
@@ -3118,7 +3142,7 @@
       </c>
       <c r="AU13" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AV13" s="3" t="inlineStr">
@@ -3128,7 +3152,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3146,7 +3170,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y2</t>
+          <t>26温州交运MTN001(资产担保)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3156,43 +3180,45 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>520449.SZ</t>
+          <t>102683428.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.50 ~ 1.79</t>
         </is>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>26温州交运MTN002</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>2.86Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>2.1185</t>
+          <t>1.7832</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3202,12 +3228,12 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>温州市交通运输集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>C- 18.13</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3217,7 +3243,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3227,50 +3253,46 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>2.02%~2.12%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X14" s="3"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币，用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+          <t>浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3" t="inlineStr">
         <is>
-          <t>天府信用增进股份有限公司</t>
+          <t>温州交运集团房地产投资开发有限公司</t>
         </is>
       </c>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3280,12 +3302,12 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3295,56 +3317,64 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK14" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK14" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>公交</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO14" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP14" s="3"/>
-      <c r="AQ14" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR14" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
           <t>有担保</t>
@@ -3352,7 +3382,7 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
@@ -3457,7 +3487,11 @@
           <t>7-</t>
         </is>
       </c>
-      <c r="X15" s="3"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>2.35%~2.45%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3592,7 +3626,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>102683462.IB</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -3803,7 +3841,9 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
@@ -3816,7 +3856,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>132600024.IB</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -4040,7 +4084,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>012682180.IB</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>0.58Y</t>
@@ -4251,7 +4299,9 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ18" s="3"/>
+      <c r="AZ18" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
@@ -4264,7 +4314,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C19" s="3"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>102683461.IB</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t>5+N</t>
@@ -4303,7 +4357,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9500/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -4484,7 +4538,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C20" s="3"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>102690021.IB</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -4523,7 +4581,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.1200</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -4708,7 +4766,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>012682178.IB</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>0.08Y</t>
@@ -4747,7 +4809,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/1.5000</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -4928,7 +4990,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>102683464.IB</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -5191,7 +5257,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1000/2.0750</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -5372,7 +5438,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>012682177.IB</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>0.16Y</t>
@@ -5411,7 +5481,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -5816,7 +5886,11 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>042680304.IB</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
           <t>0.99Y</t>
@@ -5855,7 +5929,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/1.4293</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -6303,7 +6377,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -6531,7 +6605,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -6919,7 +6993,9 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ30" s="3"/>
+      <c r="AZ30" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
@@ -7128,6 +7204,454 @@
         </is>
       </c>
       <c r="AZ31" s="3"/>
+    </row>
+    <row r="32" customHeight="true" ht="18.0">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>26振兴Y2</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>08-31 18:00</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>520449.SZ</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>5+N</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>26振兴K2</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>4.66Y</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2.1185</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>达州市振兴科技发展有限公司</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>C- 23.83</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>08-31 15:00</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>2.02%~2.12%</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>四川省-达州市</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr">
+        <is>
+          <t>天府信用增进股份有限公司</t>
+        </is>
+      </c>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr">
+        <is>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
+        </is>
+      </c>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK32" s="3"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP32" s="3"/>
+      <c r="AQ32" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>金属非金属新材料</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AZ32" s="3"/>
+    </row>
+    <row r="33" customHeight="true" ht="18.0">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>26振兴Y3</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>08-31 18:00</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>520450.SZ</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>5+N</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>1.90 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>26振兴K2</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>4.66Y</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>2.1185</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>达州市振兴科技发展有限公司</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>C- 23.83</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>08-31 15:00</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>2.17%~2.27%</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>四川省-达州市</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>成都中小企业融资担保有限责任公司</t>
+        </is>
+      </c>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr">
+        <is>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
+        </is>
+      </c>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK33" s="3"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP33" s="3"/>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>金属非金属新材料</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AZ33" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-08-31.xlsx
+++ b/data/credit_bond_all_2026-08-31.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-31" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-01" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 14.35</t>
+          <t>D+ 9.11</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -943,7 +943,9 @@
       <c r="E4" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.52</t>
@@ -983,7 +985,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 42.30</t>
+          <t>B- 42.61</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1141,7 +1143,9 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -1167,7 +1171,9 @@
       <c r="E5" s="4" t="n">
         <v>2.0</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 2.10</t>
@@ -1207,7 +1213,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 18.06</t>
+          <t>C- 18.84</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1370,68 +1376,70 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26晋能电力GN005(碳中和债)</t>
+          <t>26宁沪高MTN002</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>132680093.IB</t>
+          <t>102683460.IB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>25晋能电力MTN002</t>
+          <t>26宁沪高MTN001</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>5.38Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.9740</t>
+          <t>1.6734</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司</t>
+          <t>江苏宁沪高速公路股份有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>B- 38.73</t>
+          <t>C+ 32.25</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1451,19 +1459,19 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1474,17 +1482,17 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>山西省-太原市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
+          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
+          <t>华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
@@ -1505,7 +1513,7 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
+          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
@@ -1515,13 +1523,17 @@
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK6" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr">
@@ -1531,7 +1543,7 @@
       </c>
       <c r="AN6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO6" s="3" t="inlineStr">
@@ -1541,27 +1553,27 @@
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1586,7 +1598,7 @@
       </c>
       <c r="AY6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ6" s="3"/>
@@ -1594,7 +1606,7 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN002</t>
+          <t>26赣出版SCP004(取消发行)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1604,12 +1616,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>102683460.IB</t>
+          <t>DY012682179.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -1618,44 +1630,44 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.33 ~ 1.53</t>
         </is>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN001</t>
+          <t>25赣出版MTN001</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2.78Y</t>
+          <t>215D+1.00Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.6734</t>
+          <t>1.5317</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>1.5600/1.5300</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司</t>
+          <t>江西省出版传媒集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.91</t>
+          <t>C- 19.17</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1682,12 +1694,12 @@
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1698,23 +1710,23 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
+          <t>本期超短期融资券募集资金5亿元，拟用于偿还有息债务[26赣出版SCP002]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1729,7 +1741,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
+          <t>江西省出版传媒集团有限公司2026年度第四期超短期融资券(取消发行)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1739,12 +1751,12 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="AK7" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL7" s="3" t="inlineStr">
@@ -1769,27 +1781,27 @@
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>传媒</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>出版</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>出版</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1822,68 +1834,70 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26赣出版SCP004</t>
+          <t>26厦门产投MTN003(科创债)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>012682179.IB</t>
+          <t>102683466.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.33 ~ 1.53</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>25赣出版MTN001</t>
+          <t>26厦门产投MTN002(科创债)</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>215D+1.00Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>1.9088</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.5600/1.5300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>江西省出版传媒集团有限公司</t>
+          <t>厦门市产业投资有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 19.17</t>
+          <t>A 71.63</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1893,7 +1907,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 11:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1903,19 +1917,19 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1923,26 +1937,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z8" s="3"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元，拟用于偿还有息债务[26赣出版SCP002]</t>
+          <t>本期科技创新债券发行金额为5亿元,本期发行的募集资金扣除承销费后,拟全部用于置换发行人本期科技创新债券发行之日起一年以内用于科技创新领域股权投资或基金出资的自有资金投入。</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1957,7 +1975,7 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>江西省出版传媒集团有限公司2026年度第四期超短期融资券</t>
+          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1967,82 +1985,74 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
-        </is>
-      </c>
-      <c r="AK8" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN8" s="3" t="inlineStr">
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP8" s="3"/>
+      <c r="AQ8" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY8" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ8" s="3" t="inlineStr">
-        <is>
-          <t>传媒</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="inlineStr">
-        <is>
-          <t>出版</t>
-        </is>
-      </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>出版</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>贸易</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW8" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX8" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ8" s="3"/>
@@ -2050,7 +2060,7 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26ZTTZK1</t>
+          <t>26高教投资PPN002</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2058,60 +2068,56 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>246000.SH</t>
-        </is>
-      </c>
+      <c r="C9" s="3"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.0</v>
+        <v>4.17</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>25ZTTZK1</t>
+          <t>26高教投资PPN001</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>3.97Y</t>
+          <t>56D</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.7724</t>
+          <t>1.6401</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/1.8300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>中铁投资集团有限公司</t>
+          <t>泰州高教投资发展有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>D 4.33</t>
+          <t>B- 37.21</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2121,7 +2127,7 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -2131,128 +2137,124 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将10亿元用于偿还有息负债</t>
+          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>中铁投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ9" s="3" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AR9" s="3" t="inlineStr">
-        <is>
-          <t>专业工程</t>
-        </is>
-      </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>市政路桥</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2273,73 +2275,77 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN003(科创债)</t>
+          <t>26温州交运MTN003(资产担保)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683466.IB</t>
+          <t>102683428.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 1.79</t>
         </is>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN002(科创债)</t>
+          <t>26温州交运MTN002</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.86Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.9097</t>
+          <t>1.7832</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1.9200/1.8700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司</t>
+          <t>温州市交通运输集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>A 71.63</t>
+          <t>C- 18.13</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2349,7 +2355,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>08-31 11:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2359,50 +2365,46 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>1.82%~1.92%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X10" s="3"/>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行金额为5亿元,本期发行的募集资金扣除承销费后,拟全部用于置换发行人本期科技创新债券发行之日起一年以内用于科技创新领域股权投资或基金出资的自有资金投入。</t>
+          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币，用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD10" s="3"/>
+          <t>浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>温州交运集团房地产投资开发有限公司</t>
+        </is>
+      </c>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2417,7 +2419,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
+          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2427,13 +2429,17 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK10" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK10" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM10" s="3" t="inlineStr">
@@ -2443,33 +2449,37 @@
       </c>
       <c r="AN10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP10" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>非盈利性交运服务</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>非盈利性交运服务</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2479,7 +2489,7 @@
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW10" s="3" t="inlineStr">
@@ -2494,7 +2504,7 @@
       </c>
       <c r="AY10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ10" s="3"/>
@@ -2510,7 +2520,11 @@
           <t>08-31 11:30</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>102683458.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -2519,13 +2533,17 @@
       <c r="E11" s="4" t="n">
         <v>6.0</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>1.94 ~ 2.35</t>
         </is>
       </c>
-      <c r="H11" s="3"/>
+      <c r="H11" s="4" t="n">
+        <v>2.35</v>
+      </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -2544,12 +2562,12 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>2.3380</t>
+          <t>2.3356</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>2.3600/2.3000</t>
+          <t>2.3600/2.2800</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -2559,7 +2577,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.37</t>
+          <t>C+ 31.57</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2582,7 +2600,9 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U11" s="3"/>
+      <c r="U11" s="4" t="n">
+        <v>1.15</v>
+      </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
@@ -2726,49 +2746,55 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN002</t>
+          <t>26振兴Y1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
-        </is>
-      </c>
-      <c r="C12" s="3"/>
+          <t>08-31 19:00</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>520448.SZ</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.17</v>
+        <v>2.5</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H12" s="3"/>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>2.28</v>
+      </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN001</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>56D</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.6401</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2778,12 +2804,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.77</t>
+          <t>C- 23.83</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2793,7 +2819,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2803,46 +2829,50 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>重庆三峡融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2852,12 +2882,12 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2867,53 +2897,49 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP12" s="3"/>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2923,12 +2949,12 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -2946,53 +2972,55 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26金霞01</t>
+          <t>26晋能电力GN005(碳中和债)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>08-31 17:00</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>283880.SH</t>
+          <t>132680093.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.70 ~ 2.10</t>
         </is>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>25金霞01</t>
+          <t>25晋能电力MTN002</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>4.13Y</t>
+          <t>5.38Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.9475</t>
+          <t>1.9709</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3002,12 +3030,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>湖南金霞发展集团有限公司</t>
+          <t>晋能控股电力集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 11.49</t>
+          <t>B- 38.65</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3017,7 +3045,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3027,46 +3055,46 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>山西省-太原市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
+          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
+          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3076,93 +3104,93 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN13" s="3" t="inlineStr">
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY13" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO13" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ13" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR13" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW13" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AX13" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ13" s="3"/>
@@ -3170,70 +3198,70 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN001(资产担保)</t>
+          <t>26ZTTZK1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102683428.IB</t>
+          <t>246000.SH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.79</t>
-        </is>
-      </c>
-      <c r="H14" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1.81</v>
+      </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN002</t>
+          <t>25ZTTZK1</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2.86Y</t>
+          <t>3.97Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7832</t>
+          <t>1.7685</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8300</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司</t>
+          <t>中铁投资集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 18.13</t>
+          <t>D+ 5.33</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3243,7 +3271,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3253,61 +3281,65 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X14" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.83%~1.93%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z14" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币，用于偿还金融机构借款</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将10亿元用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>温州交运集团房地产投资开发有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
+          <t>中铁投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3317,29 +3349,25 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK14" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -3347,27 +3375,27 @@
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3377,7 +3405,7 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
@@ -3400,64 +3428,68 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26盐城创投PPN001(科创债)</t>
+          <t>26光大02(取消发行)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
-        </is>
-      </c>
-      <c r="C15" s="3"/>
+          <t>08-31 19:00</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>DY524992.SZ</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2.15 ~ 3.05</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25盐创K1</t>
+          <t>21光大集团MTN001B</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.16Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.9830</t>
+          <t>1.7413</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司</t>
+          <t>中国光大集团股份公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>D- 3.00</t>
+          <t>B- 39.61</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3467,7 +3499,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3477,95 +3509,103 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>2.35%~2.45%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z15" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
+          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
+          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
+          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>金融</t>
         </is>
       </c>
-      <c r="AP15" s="3"/>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -3573,12 +3613,12 @@
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
@@ -3611,75 +3651,75 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26江津华信MTN001</t>
+          <t>26沪盛K1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683462.IB</t>
+          <t>245999.SH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H16" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1.98</v>
+      </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>25江津华信MTN002A</t>
+          <t>26国盛MTN003(科创债)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>3.93Y</t>
+          <t>9.88Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.8922</t>
+          <t>2.0875</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0700</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司</t>
+          <t>上海国盛(集团)有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 20.11</t>
+          <t>C+ 31.23</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3689,7 +3729,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3699,46 +3739,46 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>重庆市-江津区</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
+          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3748,12 +3788,12 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
+          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3763,57 +3803,53 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK16" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2036-09-02</t>
+        </is>
+      </c>
+      <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3841,14 +3877,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ16" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ16" s="3"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN002</t>
+          <t>26盐城创投PPN001(科创债)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3856,45 +3890,41 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>132600024.IB</t>
-        </is>
-      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.5</v>
+        <v>2.0</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>2.15 ~ 3.05</t>
         </is>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN001B</t>
+          <t>25盐创K1</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.50Y</t>
+          <t>4.16Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.7922</t>
+          <t>1.9798</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3904,12 +3934,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司</t>
+          <t>盐城市创新创业投资有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.57</t>
+          <t>D- 3.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3936,43 +3966,39 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>2.35%~2.45%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
+          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中国银行股份有限公司</t>
+          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -3987,12 +4013,12 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
+          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
@@ -4008,7 +4034,7 @@
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4018,32 +4044,28 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP17" s="3"/>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4071,12 +4093,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ17" s="3"/>
+      <c r="AZ17" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26宁波能源SCP002</t>
+          <t>26江津华信MTN001</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4086,43 +4110,45 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>012682180.IB</t>
+          <t>102683462.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F18" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.70</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>GC甬能Y1</t>
+          <t>25江津华信MTN002A</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.51Y+N</t>
+          <t>3.93Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.8414</t>
+          <t>1.8922</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -4132,12 +4158,12 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.20</t>
+          <t>C- 20.51</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4164,43 +4190,39 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.64%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>重庆市-江津区</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
+          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD18" s="3" t="inlineStr">
-        <is>
-          <t>宁波开发投资集团有限公司</t>
-        </is>
-      </c>
+          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4215,7 +4237,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4225,10 +4247,14 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2027-03-30</t>
-        </is>
-      </c>
-      <c r="AK18" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -4246,32 +4272,32 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4281,7 +4307,7 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW18" s="3" t="inlineStr">
@@ -4306,7 +4332,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26太湖新城MTN010</t>
+          <t>26广州净水GN002</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4316,58 +4342,60 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683461.IB</t>
+          <t>132600024.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F19" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26太新Y3</t>
+          <t>26广州净水GN001B</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>4.93Y+N</t>
+          <t>4.50Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.8857</t>
+          <t>1.7922</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.9500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
+          <t>广州市净水有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 40.13</t>
+          <t>D+ 8.57</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4394,12 +4422,12 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4407,20 +4435,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z19" s="3"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
+          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
+          <t>广发证券股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4441,7 +4473,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
+          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4472,32 +4504,32 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4512,7 +4544,7 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
@@ -4530,7 +4562,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN003</t>
+          <t>26宁波能源SCP002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4540,58 +4572,60 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102690021.IB</t>
+          <t>012682180.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F20" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.40 ~ 1.70</t>
         </is>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN002</t>
+          <t>GC甬能Y1</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.61Y</t>
+          <t>3.51Y+N</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>2.1005</t>
+          <t>1.8509</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/2.1200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司</t>
+          <t>宁波能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C 26.57</t>
+          <t>C- 18.20</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4601,7 +4635,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>08-31 14:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4618,39 +4652,43 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>2.31%~2.41%</t>
+          <t>1.60%~1.64%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
+          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD20" s="3"/>
+          <t>宁波银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr">
+        <is>
+          <t>宁波开发投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4665,7 +4703,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
+          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4675,14 +4713,10 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK20" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-03-30</t>
+        </is>
+      </c>
+      <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -4700,7 +4734,7 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
@@ -4710,22 +4744,22 @@
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4735,7 +4769,7 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW20" s="3" t="inlineStr">
@@ -4753,12 +4787,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ20" s="3"/>
+      <c r="AZ20" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP006</t>
+          <t>26太湖新城MTN010</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4768,58 +4804,60 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>012682178.IB</t>
+          <t>102683461.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F21" s="3"/>
+      <c r="F21" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.49</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP001(科创债)</t>
+          <t>26太新Y3</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>53D</t>
+          <t>4.93Y+N</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.5142</t>
+          <t>1.8931</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.5200/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>无锡市太湖新城发展集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B- 35.15</t>
+          <t>B- 40.72</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4846,44 +4884,44 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
+          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司</t>
+          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr">
@@ -4893,7 +4931,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
+          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4903,7 +4941,7 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
@@ -4924,32 +4962,32 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -4964,7 +5002,7 @@
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
@@ -4982,7 +5020,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26新和成股MTN002(科创债)</t>
+          <t>26青城租赁MTN003</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4992,7 +5030,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>102683464.IB</t>
+          <t>102690021.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -5001,34 +5039,36 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26新和成股SCP001(科创债)</t>
+          <t>26青城租赁MTN002</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>60D</t>
+          <t>2.61Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.5159</t>
+          <t>2.1005</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5038,12 +5078,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司</t>
+          <t>青岛城乡建设融资租赁有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 25.48</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5053,7 +5093,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 14:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5070,29 +5110,33 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
-        </is>
-      </c>
-      <c r="Y22" s="3"/>
+          <t>2.31%~2.41%</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
+          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5103,7 +5147,7 @@
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -5113,7 +5157,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
+          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5148,32 +5192,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>化学制药</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5206,7 +5250,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26沪盛K1</t>
+          <t>26立讯精工SCP006</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5216,58 +5260,60 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>245999.SH</t>
+          <t>012682178.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.20 ~ 1.49</t>
         </is>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26国盛MTN003(科创债)</t>
+          <t>26立讯精工SCP001(科创债)</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>9.88Y</t>
+          <t>53D</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2.0875</t>
+          <t>1.5142</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>2.1000/2.0750</t>
+          <t>--/1.5000</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.44</t>
+          <t>B- 36.99</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5277,7 +5323,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5287,61 +5333,61 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
+          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5351,13 +5397,13 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2036-09-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
@@ -5367,7 +5413,7 @@
       </c>
       <c r="AN23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO23" s="3" t="inlineStr">
@@ -5377,27 +5423,27 @@
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5430,7 +5476,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP010</t>
+          <t>26新和成股MTN002(科创债)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5440,58 +5486,60 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>012682177.IB</t>
+          <t>102683464.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP009</t>
+          <t>26新和成股SCP001(科创债)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>50D</t>
+          <t>60D</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.4780</t>
+          <t>1.5159</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.4900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司</t>
+          <t>浙江新和成股份有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 37.31</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5518,44 +5566,40 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
+      <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
+          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5565,7 +5609,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
+          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5575,10 +5619,14 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="AK24" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK24" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5601,27 +5649,27 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>化学制药</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5654,7 +5702,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26郴新01</t>
+          <t>26华能新能SCP010</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5664,58 +5712,60 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>283833.SH</t>
+          <t>012682177.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F25" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.35 ~ 1.55</t>
         </is>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>24郴新02</t>
+          <t>26华能新能SCP009</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>3.14Y</t>
+          <t>50D</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>2.2484</t>
+          <t>1.4780</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司</t>
+          <t>华能新能源股份有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.49</t>
+          <t>B- 39.39</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5725,7 +5775,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5735,77 +5785,77 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>2.40%~2.50%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>湖南省-郴州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
+          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
@@ -5815,37 +5865,37 @@
       </c>
       <c r="AN25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5899,7 +5949,9 @@
       <c r="E26" s="4" t="n">
         <v>20.0</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
           <t>1.37 ~ 1.67</t>
@@ -5939,7 +5991,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>B- 45.61</t>
+          <t>B- 44.10</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6102,7 +6154,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y1</t>
+          <t>26江宁滨江PPN002</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6110,45 +6162,41 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>520448.SZ</t>
-        </is>
-      </c>
+      <c r="C27" s="3"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>25江宁滨江PPN004</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>2.18Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2.1185</t>
+          <t>1.8442</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -6158,12 +6206,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>南京江宁滨江新城开发建设有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>C 25.72</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6173,7 +6221,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6183,50 +6231,46 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD27" s="3" t="inlineStr">
-        <is>
-          <t>重庆三峡融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6236,12 +6280,12 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
+          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6251,64 +6295,68 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>8*无效</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM27" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO27" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP27" s="3"/>
-      <c r="AQ27" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR27" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS27" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT27" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU27" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
@@ -6321,12 +6369,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ27" s="3"/>
+      <c r="AZ27" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26光大01</t>
+          <t>26无锡城南PPN001(取消发行)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6334,60 +6384,48 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>524991.SZ</t>
-        </is>
-      </c>
+      <c r="C28" s="3"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>20.0</v>
+        <v>3.6</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>24光大集团MTN004A</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>2.84Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6671</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司</t>
+          <t>无锡市城南建设投资发展有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 40.88</t>
+          <t>C+ 32.48</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6397,7 +6435,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6407,81 +6445,73 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t>1.61%~1.71%</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X28" s="3"/>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
+          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="AK28" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
@@ -6491,37 +6521,37 @@
       </c>
       <c r="AN28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6554,7 +6584,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26光大02</t>
+          <t>26振兴Y3</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6564,58 +6594,60 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>524992.SZ</t>
+          <t>520450.SZ</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>20.0</v>
+        <v>2.5</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H29" s="3"/>
+          <t>1.90 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>2.35</v>
+      </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>21光大集团MTN001B</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7413</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>B- 40.88</t>
+          <t>C- 23.83</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6642,36 +6674,40 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.17%~2.27%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD29" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr">
+        <is>
+          <t>成都中小企业融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE29" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -6679,7 +6715,7 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
@@ -6689,12 +6725,12 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
@@ -6720,32 +6756,28 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP29" s="3"/>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6755,12 +6787,12 @@
       </c>
       <c r="AV29" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -6778,64 +6810,70 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26江宁滨江PPN002</t>
+          <t>26光大01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
-        </is>
-      </c>
-      <c r="C30" s="3"/>
+          <t>08-31 19:00</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>524991.SZ</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.3</v>
+        <v>20.0</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H30" s="3"/>
+          <t>1.10 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1.55</v>
+      </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>25江宁滨江PPN004</t>
+          <t>24光大集团MTN004A</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.18Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.8442</t>
+          <t>1.6671</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司</t>
+          <t>中国光大集团股份公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 26.09</t>
+          <t>B- 39.61</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6845,7 +6883,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6855,117 +6893,125 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z30" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
+          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
+          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
+          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
-        </is>
-      </c>
-      <c r="AK30" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK30" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>8*无效</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -6993,118 +7039,134 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ30" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ30" s="3"/>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26无锡城南PPN001(取消发行)</t>
+          <t>26开滦Y1</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
-        </is>
-      </c>
-      <c r="C31" s="3"/>
+          <t>08-31 19:00</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>245986.SH</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.6</v>
+        <v>10.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H31" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>1.99</v>
+      </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>25开滦MTN001(科创票据)</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>1.38Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>1.8119</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>开滦(集团)有限责任公司</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>C 29.29</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>08-31 15:00</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>无锡市城南建设投资发展有限公司</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>B- 39.79</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>08-31 09:00</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X31" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>1.94%~2.04%</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7114,68 +7176,72 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
+          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK31" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK31" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7190,7 +7256,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7208,53 +7274,55 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y2</t>
+          <t>26郴新01</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>520449.SZ</t>
+          <t>283833.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.0</v>
+        <v>2.78</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
-        </is>
-      </c>
-      <c r="H32" s="3"/>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>2.33</v>
+      </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>24郴新02</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>3.14Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2.1185</t>
+          <t>2.2500</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7264,12 +7332,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>郴州市新天投资有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>C+ 33.49</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7279,7 +7347,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7296,40 +7364,36 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>2.02%~2.12%</t>
+          <t>2.40%~2.50%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>湖南省-郴州市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD32" s="3" t="inlineStr">
-        <is>
-          <t>天府信用增进股份有限公司</t>
-        </is>
-      </c>
+          <t>财信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7342,12 +7406,12 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7378,28 +7442,32 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP32" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>金属非金属新材料</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7409,12 +7477,12 @@
       </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7432,17 +7500,17 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y3</t>
+          <t>26振兴Y2</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>520450.SZ</t>
+          <t>520449.SZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7451,19 +7519,21 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.5</v>
+        <v>3.0</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H33" s="3"/>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>2.28</v>
+      </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -7478,7 +7548,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2.1185</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7525,7 +7595,7 @@
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>2.02%~2.12%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7551,7 +7621,7 @@
       </c>
       <c r="AD33" s="3" t="inlineStr">
         <is>
-          <t>成都中小企业融资担保有限责任公司</t>
+          <t>天府信用增进股份有限公司</t>
         </is>
       </c>
       <c r="AE33" s="3" t="inlineStr">
@@ -7571,7 +7641,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7652,6 +7722,232 @@
         </is>
       </c>
       <c r="AZ33" s="3"/>
+    </row>
+    <row r="34" customHeight="true" ht="18.0">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>26金霞01</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>08-31 19:00</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>283880.SH</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>25金霞01</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>4.13Y</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1.9567</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>湖南金霞发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>C- 11.49</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>08-31 15:00</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.80%~1.90%</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>湖南省-长沙市</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AZ34" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-08-31.xlsx
+++ b/data/credit_bond_all_2026-08-31.xlsx
@@ -721,7 +721,9 @@
           <t>1.50 ~ 2.20</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.85</v>
+      </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -778,8 +780,12 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>5.38</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>6+</t>
@@ -951,7 +957,9 @@
           <t>1.30 ~ 1.52</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.42</v>
+      </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -1008,8 +1016,12 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1143,9 +1155,7 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ4" s="4" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="AZ4" s="3"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -1179,7 +1189,9 @@
           <t>1.30 ~ 2.10</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.6</v>
+      </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -1236,8 +1248,12 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
+      <c r="U5" s="4" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -1405,7 +1421,9 @@
           <t>1.40 ~ 2.00</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.54</v>
+      </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1462,8 +1480,12 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+      <c r="U6" s="4" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -1887,7 +1909,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9000/1.8800</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -2083,7 +2105,9 @@
           <t>1.40 ~ 2.20</t>
         </is>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -2140,8 +2164,12 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
+      <c r="U9" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
           <t>8+</t>
@@ -2275,9 +2303,7 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ9" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ9" s="3"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
@@ -2746,55 +2772,55 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y1</t>
+          <t>26晋能电力GN005(碳中和债)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>520448.SZ</t>
+          <t>132680093.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>2.28</v>
-      </c>
+          <t>1.70 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>25晋能电力MTN002</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>5.38Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.9709</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2804,12 +2830,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>晋能控股电力集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>B- 38.65</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2819,7 +2845,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2836,43 +2862,39 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>山西省-太原市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>重庆三峡融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2882,17 +2904,17 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
+          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
@@ -2903,58 +2925,62 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP12" s="3"/>
-      <c r="AQ12" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -2964,7 +2990,7 @@
       </c>
       <c r="AY12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AZ12" s="3"/>
@@ -2972,17 +2998,17 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26晋能电力GN005(碳中和债)</t>
+          <t>26ZTTZK1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>132680093.IB</t>
+          <t>246000.SH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -2991,51 +3017,51 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H13" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1.81</v>
+      </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>25晋能电力MTN002</t>
+          <t>25ZTTZK1</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>5.38Y</t>
+          <t>3.97Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.9709</t>
+          <t>1.7685</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8300</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司</t>
+          <t>中铁投资集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 38.65</t>
+          <t>D+ 5.33</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3045,7 +3071,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3067,7 +3093,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3075,41 +3101,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z13" s="3"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>山西省-太原市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将10亿元用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
+          <t>中铁投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3125,7 +3155,7 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
@@ -3145,27 +3175,27 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3190,7 +3220,7 @@
       </c>
       <c r="AY13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ13" s="3"/>
@@ -3198,7 +3228,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26ZTTZK1</t>
+          <t>26光大02(取消发行)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3208,7 +3238,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>246000.SH</t>
+          <t>DY524992.SZ</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3217,51 +3247,49 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>1.81</v>
-      </c>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25ZTTZK1</t>
+          <t>21光大集团MTN001B</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>3.97Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7685</t>
+          <t>1.7413</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/1.8300</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>中铁投资集团有限公司</t>
+          <t>中国光大集团股份公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.33</t>
+          <t>B- 39.61</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3271,7 +3299,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3288,12 +3316,12 @@
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3313,12 +3341,12 @@
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将10亿元用于偿还有息负债</t>
+          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
+          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3329,17 +3357,17 @@
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>中铁投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3370,32 +3398,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3428,100 +3456,104 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26光大02(取消发行)</t>
+          <t>26沪盛K1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>DY524992.SZ</t>
+          <t>245999.SH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H15" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1.98</v>
+      </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>26国盛MTN003(科创债)</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>9.88Y</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>2.0875</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>--/2.0700</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>上海国盛(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>C+ 31.23</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>08-31 16:00</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>21光大集团MTN001B</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>4.95Y</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>1.7413</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>1.7600/--</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>中国光大集团股份公司</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>B- 39.61</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>08-31 15:00</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U15" s="3"/>
+      <c r="U15" s="4" t="n">
+        <v>3.9</v>
+      </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3529,24 +3561,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
@@ -3557,17 +3585,17 @@
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)(取消发行)</t>
+          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3577,7 +3605,7 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2036-09-02</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
@@ -3598,27 +3626,27 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
@@ -3656,70 +3684,70 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26沪盛K1</t>
+          <t>26振兴Y3</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:30</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>245999.SH</t>
+          <t>520450.SZ</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10.0</v>
+        <v>2.5</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.90 ~ 3.00</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26国盛MTN003(科创债)</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>9.88Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2.0875</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/2.0700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.23</t>
+          <t>C- 23.83</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3729,7 +3757,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3746,36 +3774,40 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>2.17%~2.27%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>成都中小企业融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3788,22 +3820,22 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2036-09-02</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3827,11 +3859,7 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
+      <c r="AP16" s="3"/>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -3839,17 +3867,17 @@
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3859,12 +3887,12 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3882,49 +3910,55 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26盐城创投PPN001(科创债)</t>
+          <t>26振兴Y1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
-        </is>
-      </c>
-      <c r="C17" s="3"/>
+          <t>08-31 19:00</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>520448.SZ</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.0</v>
+        <v>2.5</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2.15 ~ 3.05</t>
-        </is>
-      </c>
-      <c r="H17" s="3"/>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>2.28</v>
+      </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25盐创K1</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.16Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.9798</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3934,12 +3968,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>D- 3.00</t>
+          <t>C- 23.83</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3949,7 +3983,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -3959,19 +3993,19 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>2.35%~2.45%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -3982,23 +4016,27 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD17" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr">
+        <is>
+          <t>重庆三峡融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4008,12 +4046,12 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4023,49 +4061,49 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP17" s="3"/>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4075,12 +4113,12 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4093,14 +4131,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ17" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ17" s="3"/>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26江津华信MTN001</t>
+          <t>26盐城创投PPN001(科创债)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4108,47 +4144,41 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>102683462.IB</t>
-        </is>
-      </c>
+      <c r="C18" s="3"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>2.15 ~ 3.05</t>
         </is>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25江津华信MTN002A</t>
+          <t>25盐创K1</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.93Y</t>
+          <t>4.16Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.8922</t>
+          <t>1.9798</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -4158,12 +4188,12 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司</t>
+          <t>盐城市创新创业投资有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 20.51</t>
+          <t>D- 3.00</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4190,12 +4220,12 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>2.35%~2.45%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4206,23 +4236,23 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>重庆市-江津区</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
+          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
+          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4237,24 +4267,20 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
+          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -4262,7 +4288,7 @@
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
@@ -4272,32 +4298,28 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP18" s="3"/>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4332,7 +4354,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN002</t>
+          <t>26江津华信MTN001</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4342,45 +4364,47 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>132600024.IB</t>
+          <t>102683462.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.5</v>
+        <v>3.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.5</v>
+        <v>3.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H19" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>1.78</v>
+      </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN001B</t>
+          <t>25江津华信MTN002A</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>4.50Y</t>
+          <t>3.93Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.7922</t>
+          <t>1.8922</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4390,12 +4414,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.57</t>
+          <t>C- 20.51</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4418,41 +4442,41 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
+      <c r="U19" s="4" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>重庆市-江津区</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
+          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中国银行股份有限公司</t>
+          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4473,7 +4497,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4483,10 +4507,14 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK19" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK19" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -4504,32 +4532,32 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4562,7 +4590,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26宁波能源SCP002</t>
+          <t>26广州净水GN002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4572,45 +4600,47 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>012682180.IB</t>
+          <t>132600024.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H20" s="3"/>
+          <t>1.40 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1.71</v>
+      </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>GC甬能Y1</t>
+          <t>26广州净水GN001B</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>3.51Y+N</t>
+          <t>4.50Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.8509</t>
+          <t>1.7922</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4620,12 +4650,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司</t>
+          <t>广州市净水有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 18.20</t>
+          <t>D+ 8.57</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4648,47 +4678,49 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U20" s="3"/>
+      <c r="U20" s="4" t="n">
+        <v>5.44</v>
+      </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.64%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z20" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
+          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD20" s="3" t="inlineStr">
-        <is>
-          <t>宁波开发投资集团有限公司</t>
-        </is>
-      </c>
+          <t>广发证券股份有限公司,中国银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4703,7 +4735,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券</t>
+          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4713,7 +4745,7 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2027-03-30</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4739,7 +4771,7 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
@@ -4749,17 +4781,17 @@
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4769,7 +4801,7 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW20" s="3" t="inlineStr">
@@ -4787,14 +4819,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ20" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ20" s="3"/>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26太湖新城MTN010</t>
+          <t>26宁波能源SCP002</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4804,45 +4834,45 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683461.IB</t>
+          <t>012682180.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 1.70</t>
         </is>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26太新Y3</t>
+          <t>GC甬能Y1</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>4.93Y+N</t>
+          <t>3.51Y+N</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.8931</t>
+          <t>1.8509</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4852,12 +4882,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
+          <t>宁波能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B- 40.72</t>
+          <t>C- 18.20</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4884,39 +4914,43 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.60%~1.64%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
+          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD21" s="3"/>
+          <t>宁波银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>宁波开发投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4931,7 +4965,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
+          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4941,7 +4975,7 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2027-03-30</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
@@ -4962,32 +4996,32 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -4997,12 +5031,12 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
@@ -5015,12 +5049,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN003</t>
+          <t>26太湖新城MTN010</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5030,45 +5066,47 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>102690021.IB</t>
+          <t>102683461.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1.98</v>
+      </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN002</t>
+          <t>26太新Y3</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.61Y</t>
+          <t>4.93Y+N</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2.1005</t>
+          <t>1.8931</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5078,12 +5116,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司</t>
+          <t>无锡市太湖新城发展集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C 25.48</t>
+          <t>B- 40.72</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5093,7 +5131,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>08-31 14:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5106,37 +5144,41 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>1.92</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>2.31%~2.41%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
+          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
+          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5157,7 +5199,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
+          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5167,14 +5209,10 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK22" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5192,32 +5230,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5232,7 +5270,7 @@
       </c>
       <c r="AW22" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX22" s="3" t="inlineStr">
@@ -5250,7 +5288,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP006</t>
+          <t>26青城租赁MTN003</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5260,60 +5298,62 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>012682178.IB</t>
+          <t>102690021.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.49</t>
-        </is>
-      </c>
-      <c r="H23" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>2.1</v>
+      </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP001(科创债)</t>
+          <t>26青城租赁MTN002</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>53D</t>
+          <t>2.61Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.5142</t>
+          <t>2.1005</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>青岛城乡建设融资租赁有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B- 36.99</t>
+          <t>C 25.48</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5323,7 +5363,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 14:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5336,16 +5376,20 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
+      <c r="U23" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>2.31%~2.41%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5356,28 +5400,28 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
+          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
@@ -5387,7 +5431,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
+          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5397,10 +5441,14 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AK23" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5418,32 +5466,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5476,7 +5524,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26新和成股MTN002(科创债)</t>
+          <t>26立讯精工SCP006</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5486,12 +5534,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683464.IB</t>
+          <t>012682178.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -5502,44 +5550,46 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H24" s="3"/>
+          <t>1.20 ~ 1.49</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1.49</v>
+      </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26新和成股SCP001(科创债)</t>
+          <t>26立讯精工SCP001(科创债)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>60D</t>
+          <t>53D</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.5159</t>
+          <t>1.5142</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5000</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 36.99</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5562,39 +5612,45 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U24" s="3"/>
+      <c r="U24" s="4" t="n">
+        <v>0.92</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
-        </is>
-      </c>
-      <c r="Y24" s="3"/>
+          <t>1.49%~1.53%</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
+          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5609,7 +5665,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
+          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5619,14 +5675,10 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5649,27 +5701,27 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>化学制药</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5702,7 +5754,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP010</t>
+          <t>26新和成股MTN002(科创债)</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5712,60 +5764,62 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>012682177.IB</t>
+          <t>102683464.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
-        </is>
-      </c>
-      <c r="H25" s="3"/>
+          <t>1.50 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1.6</v>
+      </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP009</t>
+          <t>26新和成股SCP001(科创债)</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>50D</t>
+          <t>60D</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.4780</t>
+          <t>1.5159</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.4900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司</t>
+          <t>浙江新和成股份有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>B- 39.39</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5788,48 +5842,48 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
+      <c r="U25" s="4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>1.17</v>
+      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
+      <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
+          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5839,7 +5893,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
+          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5849,10 +5903,14 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="AK25" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5875,27 +5933,27 @@
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>化学制药</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5928,7 +5986,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26苏交通CP005</t>
+          <t>26华能新能SCP010</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5938,12 +5996,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>042680304.IB</t>
+          <t>012682177.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0.99Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -5954,44 +6012,46 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.37 ~ 1.67</t>
-        </is>
-      </c>
-      <c r="H26" s="3"/>
+          <t>1.35 ~ 1.55</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1.38</v>
+      </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26苏交通CP004</t>
+          <t>26华能新能SCP009</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>354D</t>
+          <t>50D</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>1.4780</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.4293</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司</t>
+          <t>华能新能源股份有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>B- 44.10</t>
+          <t>B- 39.39</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6014,16 +6074,20 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+      <c r="U26" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6034,28 +6098,28 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
+          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,杭州银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -6065,7 +6129,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司2026年度第五期短期融资券</t>
+          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6075,7 +6139,7 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2027-08-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6096,32 +6160,32 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6154,7 +6218,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26江宁滨江PPN002</t>
+          <t>26苏交通CP005</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6162,56 +6226,64 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>042680304.IB</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.99Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H27" s="3"/>
+          <t>1.37 ~ 1.67</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.42</v>
+      </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>25江宁滨江PPN004</t>
+          <t>26苏交通CP004</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.18Y</t>
+          <t>354D</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.8442</t>
+          <t>1.5317</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/1.4293</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司</t>
+          <t>江苏交通控股有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C 25.72</t>
+          <t>B- 44.10</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6234,43 +6306,47 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
+      <c r="U27" s="4" t="n">
+        <v>2.985</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
+          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6285,17 +6361,17 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
+          <t>江苏交通控股有限公司2026年度第五期短期融资券</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2027-08-27</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
@@ -6316,12 +6392,12 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>8*无效</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
@@ -6331,17 +6407,17 @@
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6369,14 +6445,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ27" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ27" s="3"/>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26无锡城南PPN001(取消发行)</t>
+          <t>26江宁滨江PPN002</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6387,94 +6461,112 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H28" s="3"/>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1.73</v>
+      </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>25江宁滨江PPN004</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>2.18Y</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>1.8442</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>南京江宁滨江新城开发建设有限公司</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>C 25.72</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>08-31 09:00</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>无锡市城南建设投资发展有限公司</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t>C+ 32.48</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>08-31 09:00</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
+      <c r="U28" s="4" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X28" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>1.88%~1.98%</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
+          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6495,7 +6587,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
+          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6505,7 +6597,7 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
@@ -6531,7 +6623,7 @@
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8*无效</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
@@ -6541,12 +6633,12 @@
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
@@ -6584,7 +6676,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y3</t>
+          <t>26无锡城南PPN001(取消发行)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6592,47 +6684,33 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>520450.SZ</t>
-        </is>
-      </c>
+      <c r="C29" s="3"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>2.35</v>
-      </c>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>26振兴K2</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>4.66Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6642,12 +6720,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>无锡市城南建设投资发展有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>C+ 32.48</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6657,7 +6735,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6667,21 +6745,17 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t>2.17%~2.27%</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X29" s="3"/>
       <c r="Y29" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6690,27 +6764,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD29" s="3" t="inlineStr">
-        <is>
-          <t>成都中小企业融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>江苏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6720,12 +6790,12 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
+          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6735,64 +6805,68 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM29" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO29" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP29" s="3"/>
-      <c r="AQ29" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR29" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV29" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-31.xlsx
+++ b/data/credit_bond_all_2026-08-31.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-01" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-02" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26高淳国资MTN001</t>
+          <t>26知识城SCP002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,62 +702,62 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>102690020.IB</t>
+          <t>012682176.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.27Y</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.30 ~ 1.52</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25高淳国资MTN002</t>
+          <t>26知识城SCP001</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>3.63Y+N</t>
+          <t>122D</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.9715</t>
+          <t>1.5318</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/1.8700</t>
+          <t>1.5300/1.5000</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司</t>
+          <t>知识城(广州)投资集团有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.11</t>
+          <t>B- 40.67</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -781,46 +781,46 @@
         </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>5.05</v>
+        <v>1.79</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>5.38</v>
+        <v>1.0</v>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
+          <t>本期超短期融资券基础发行规模0亿元,发行金额上限10亿元(含),用于偿还债务融资工具[25知识城SCP007]</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
+          <t>浙商银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
+          <t>知识城(广州)投资集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -845,14 +845,10 @@
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK3" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="AK3" s="3"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -860,7 +856,7 @@
       </c>
       <c r="AM3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN3" s="3" t="inlineStr">
@@ -870,34 +866,34 @@
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>房屋建设</t>
-        </is>
-      </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
           <t/>
@@ -910,7 +906,7 @@
       </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX3" s="3" t="inlineStr">
@@ -923,12 +919,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ3" s="3"/>
+      <c r="AZ3" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26知识城SCP002</t>
+          <t>26赣出版SCP004(取消发行)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -938,62 +936,58 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>012682176.IB</t>
+          <t>DY012682179.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.27Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.52</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>1.42</v>
-      </c>
+          <t>1.33 ~ 1.53</t>
+        </is>
+      </c>
+      <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26知识城SCP001</t>
+          <t>25赣出版MTN001</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>122D</t>
+          <t>215D+1.00Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.5318</t>
+          <t>1.5317</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.5000</t>
+          <t>1.5600/1.5300</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>知识城(广州)投资集团有限公司</t>
+          <t>江西省出版传媒集团有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 42.61</t>
+          <t>C- 19.17</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1016,20 +1010,16 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U4" s="4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>1.0</v>
-      </c>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1040,17 +1030,17 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行规模0亿元,发行金额上限10亿元(含),用于偿还债务融资工具[25知识城SCP007]</t>
+          <t>本期超短期融资券募集资金5亿元，拟用于偿还有息债务[26赣出版SCP002]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,渤海银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
@@ -1071,7 +1061,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>知识城(广州)投资集团有限公司2026年度第二期超短期融资券</t>
+          <t>江西省出版传媒集团有限公司2026年度第四期超短期融资券(取消发行)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1081,10 +1071,14 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="AK4" s="3"/>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -1102,32 +1096,32 @@
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>传媒</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>出版</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>出版</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
@@ -1160,72 +1154,70 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN005</t>
+          <t>26厦门产投MTN003(科创债)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>102683459.IB</t>
+          <t>102683466.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>1.6</v>
-      </c>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>25淮安国投MTN003</t>
+          <t>26厦门产投MTN002(科创债)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>1.66Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.6367</t>
+          <t>1.9088</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/1.6000</t>
+          <t>1.8950/1.8800</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>厦门市产业投资有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 18.84</t>
+          <t>A 71.63</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1235,7 +1227,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 11:00</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1245,15 +1237,11 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>2.0</v>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -1261,7 +1249,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1269,20 +1257,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z5" s="3"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元,本次中期票据募集资金拟全部用于偿还发行人到期债券。[23 淮安国投MTN004]</t>
+          <t>本期科技创新债券发行金额为5亿元,本期发行的募集资金扣除承销费后,拟全部用于置换发行人本期科技创新债券发行之日起一年以内用于科技创新领域股权投资或基金出资的自有资金投入。</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司</t>
+          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
@@ -1303,7 +1295,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年度第五期中期票据</t>
+          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1313,78 +1305,74 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN5" s="3" t="inlineStr">
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP5" s="3"/>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY5" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO5" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ5" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR5" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX5" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ5" s="3"/>
@@ -1392,72 +1380,72 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN002</t>
+          <t>26越秀集团MTN004(绿色)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 11:30</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>102683460.IB</t>
+          <t>102683458.IB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.94 ~ 2.35</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.54</v>
+        <v>2.35</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN001</t>
+          <t>26广越12</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2.78Y</t>
+          <t>9.98Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.6734</t>
+          <t>2.3356</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>2.3500/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司</t>
+          <t>广州越秀集团股份有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.25</t>
+          <t>C+ 30.55</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1477,15 +1465,13 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U6" s="4" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>1.15</v>
+      </c>
+      <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -1493,7 +1479,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>2.24%~2.34%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1504,17 +1490,17 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
+          <t>发行人拟将本期绿色中期票据募集资金6亿元用于偿还发行人有息债务[21越秀集团GN002（革命老区）]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司</t>
+          <t>中国银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
@@ -1535,7 +1521,7 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
+          <t>广州越秀集团股份有限公司2026年度第四期绿色中期票据</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
@@ -1545,17 +1531,17 @@
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>2036-08-31</t>
         </is>
       </c>
       <c r="AK6" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr">
@@ -1565,7 +1551,7 @@
       </c>
       <c r="AN6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO6" s="3" t="inlineStr">
@@ -1575,27 +1561,27 @@
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1628,68 +1614,70 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26赣出版SCP004(取消发行)</t>
+          <t>26晋能电力GN005(碳中和债)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>DY012682179.IB</t>
+          <t>132680093.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.33 ~ 1.53</t>
+          <t>1.70 ~ 2.10</t>
         </is>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>25赣出版MTN001</t>
+          <t>25晋能电力MTN002</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>215D+1.00Y</t>
+          <t>5.38Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>1.9709</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>1.5600/1.5300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>江西省出版传媒集团有限公司</t>
+          <t>晋能控股电力集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C- 19.17</t>
+          <t>B- 36.86</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1709,19 +1697,19 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1732,23 +1720,23 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>山西省-太原市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元，拟用于偿还有息债务[26赣出版SCP002]</t>
+          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1763,7 +1751,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>江西省出版传媒集团有限公司2026年度第四期超短期融资券(取消发行)</t>
+          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1773,82 +1761,78 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
-        </is>
-      </c>
-      <c r="AK7" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN7" s="3" t="inlineStr">
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY7" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO7" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ7" s="3" t="inlineStr">
-        <is>
-          <t>传媒</t>
-        </is>
-      </c>
-      <c r="AR7" s="3" t="inlineStr">
-        <is>
-          <t>出版</t>
-        </is>
-      </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>出版</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>贸易</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX7" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ7" s="3"/>
@@ -1856,17 +1840,17 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN003(科创债)</t>
+          <t>26ZTTZK1</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>102683466.IB</t>
+          <t>246000.SH</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1875,51 +1859,51 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H8" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1.81</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN002(科创债)</t>
+          <t>25ZTTZK1</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>3.97Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.9088</t>
+          <t>1.7685</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.9000/1.8800</t>
+          <t>--/1.8300</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司</t>
+          <t>中铁投资集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>A 71.63</t>
+          <t>D+ 5.33</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1929,7 +1913,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>08-31 11:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1951,7 +1935,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1966,38 +1950,38 @@
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行金额为5亿元,本期发行的募集资金扣除承销费后,拟全部用于置换发行人本期科技创新债券发行之日起一年以内用于科技创新领域股权投资或基金出资的自有资金投入。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将10亿元用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
+          <t>中铁投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -2013,7 +1997,7 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AM8" s="3" t="inlineStr">
@@ -2028,28 +2012,32 @@
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP8" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2074,7 +2062,7 @@
       </c>
       <c r="AY8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ8" s="3"/>
@@ -2082,66 +2070,68 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN002</t>
+          <t>26光大02(取消发行)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
-        </is>
-      </c>
-      <c r="C9" s="3"/>
+          <t>08-31 19:00</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>DY524992.SZ</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.17</v>
+        <v>20.0</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>1.8</v>
-      </c>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN001</t>
+          <t>21光大集团MTN001B</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>56D</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.6401</t>
+          <t>1.7413</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司</t>
+          <t>中国光大集团股份公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>B- 37.21</t>
+          <t>B- 38.65</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2151,7 +2141,7 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -2161,121 +2151,121 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>1.2</v>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z9" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
+          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
+          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2308,70 +2298,70 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN003(资产担保)</t>
+          <t>26沪盛K1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683428.IB</t>
+          <t>245999.SH</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.79</t>
-        </is>
-      </c>
-      <c r="H10" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1.98</v>
+      </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN002</t>
+          <t>26国盛MTN003(科创债)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2.86Y</t>
+          <t>9.88Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.7832</t>
+          <t>2.0875</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0700</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司</t>
+          <t>上海国盛(集团)有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 18.13</t>
+          <t>C 29.01</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2381,7 +2371,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2391,46 +2381,48 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U10" s="3"/>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>3.9</v>
+      </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X10" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>2.04%~2.14%</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币，用于偿还金融机构借款</t>
+          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>温州交运集团房地产投资开发有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2440,12 +2432,12 @@
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
+          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2455,29 +2447,25 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK10" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2036-09-02</t>
+        </is>
+      </c>
+      <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -2485,27 +2473,27 @@
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2515,7 +2503,7 @@
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW10" s="3" t="inlineStr">
@@ -2538,33 +2526,31 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN004(绿色)</t>
+          <t>26振兴Y3</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>08-31 11:30</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>102683458.IB</t>
+          <t>520450.SZ</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>6.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.94 ~ 2.35</t>
+          <t>1.90 ~ 3.00</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
@@ -2573,37 +2559,37 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26广越12</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>9.98Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>2.3356</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>2.3600/2.2800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.57</t>
+          <t>C- 23.83</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2613,7 +2599,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2623,48 +2609,50 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>1.15</v>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>2.24%~2.34%</t>
+          <t>2.17%~2.27%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期绿色中期票据募集资金6亿元用于偿还发行人有息债务[21越秀集团GN002（革命老区）]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD11" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>成都中小企业融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2674,32 +2662,28 @@
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第四期绿色中期票据</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2036-08-31</t>
-        </is>
-      </c>
-      <c r="AK11" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
@@ -2709,7 +2693,7 @@
       </c>
       <c r="AN11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AO11" s="3" t="inlineStr">
@@ -2717,11 +2701,7 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+      <c r="AP11" s="3"/>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -2729,17 +2709,17 @@
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2749,12 +2729,12 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -2772,55 +2752,55 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26晋能电力GN005(碳中和债)</t>
+          <t>26振兴Y1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>132680093.IB</t>
+          <t>520448.SZ</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H12" s="3"/>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>2.28</v>
+      </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>25晋能电力MTN002</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>5.38Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.9709</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2830,12 +2810,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 38.65</t>
+          <t>C- 23.83</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2845,7 +2825,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2862,39 +2842,43 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>山西省-太原市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>重庆三峡融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2904,17 +2888,17 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
@@ -2925,7 +2909,7 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AM12" s="3" t="inlineStr">
@@ -2943,29 +2927,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP12" s="3"/>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2975,12 +2955,12 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -2990,7 +2970,7 @@
       </c>
       <c r="AY12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ12" s="3"/>
@@ -2998,70 +2978,72 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26ZTTZK1</t>
+          <t>26宁沪高MTN002</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>246000.SH</t>
+          <t>102683460.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>25ZTTZK1</t>
+          <t>26宁沪高MTN001</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>3.97Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.7685</t>
+          <t>1.6734</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/1.8300</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>中铁投资集团有限公司</t>
+          <t>江苏宁沪高速公路股份有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.33</t>
+          <t>C+ 30.91</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3071,7 +3053,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3081,19 +3063,23 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3101,45 +3087,41 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将10亿元用于偿还有息负债</t>
+          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
+          <t>华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>中铁投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3149,13 +3131,17 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK13" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
@@ -3165,7 +3151,7 @@
       </c>
       <c r="AN13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO13" s="3" t="inlineStr">
@@ -3175,27 +3161,27 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3228,209 +3214,213 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26光大02(取消发行)</t>
+          <t>26江宁滨江PPN002</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>DY524992.SZ</t>
+          <t>032680505.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>2.3</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>2.3</v>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H14" s="3"/>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1.73</v>
+      </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>25江宁滨江PPN004</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>2.18Y</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>1.8442</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>南京江宁滨江新城开发建设有限公司</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>C- 24.12</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>08-31 09:00</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>21光大集团MTN001B</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>4.95Y</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>1.7413</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>1.7600/--</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>中国光大集团股份公司</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>B- 39.61</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>08-31 15:00</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)(取消发行)</t>
+          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>8*无效</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO14" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ14" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR14" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3451,75 +3441,79 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26沪盛K1</t>
+          <t>26温州交运MTN003(资产担保)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:30</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>245999.SH</t>
+          <t>102683428.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F15" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 1.79</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26国盛MTN003(科创债)</t>
+          <t>26温州交运MTN002</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>9.88Y</t>
+          <t>2.86Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>2.0875</t>
+          <t>1.7832</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/2.0700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司</t>
+          <t>温州市交通运输集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.23</t>
+          <t>C- 18.84</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3529,7 +3523,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3539,48 +3533,46 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="n">
-        <v>3.9</v>
-      </c>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>2.04%~2.14%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X15" s="3"/>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
+          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币，用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD15" s="3"/>
+          <t>浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr">
+        <is>
+          <t>温州交运集团房地产投资开发有限公司</t>
+        </is>
+      </c>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3590,12 +3582,12 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3605,63 +3597,67 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2036-09-02</t>
-        </is>
-      </c>
-      <c r="AK15" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK15" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>公交</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO15" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="AQ15" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR15" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW15" s="3" t="inlineStr">
@@ -3684,55 +3680,57 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y3</t>
+          <t>26盐城创投PPN001(混合型科创债)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>520450.SZ</t>
+          <t>032680495.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F16" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 3.00</t>
+          <t>2.15 ~ 3.05</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>25盐创K1</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>4.16Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.9798</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3742,12 +3740,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>盐城市创新创业投资有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>D- 1.50</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3757,7 +3755,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3767,19 +3765,19 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>2.35%~2.45%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3790,27 +3788,23 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>成都中小企业融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3820,12 +3814,12 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
+          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3835,51 +3829,51 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP16" s="3"/>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR16" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS16" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
       <c r="AU16" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3887,12 +3881,12 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3905,22 +3899,24 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y1</t>
+          <t>26太湖新城MTN010</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>520448.SZ</t>
+          <t>102683461.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3929,36 +3925,38 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>26太新Y3</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>4.93Y+N</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.8931</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3968,12 +3966,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>无锡市太湖新城发展集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>B- 35.06</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3983,7 +3981,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -3993,50 +3991,50 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>1.92</v>
+      </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD17" s="3" t="inlineStr">
-        <is>
-          <t>重庆三峡融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4046,74 +4044,78 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
+          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO17" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP17" s="3"/>
-      <c r="AQ17" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR17" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW17" s="3" t="inlineStr">
@@ -4136,7 +4138,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26盐城创投PPN001(科创债)</t>
+          <t>26高淳国资MTN001</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4144,56 +4146,64 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>102690020.IB</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F18" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2.15 ~ 3.05</t>
-        </is>
-      </c>
-      <c r="H18" s="3"/>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1.85</v>
+      </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25盐创K1</t>
+          <t>25高淳国资MTN002</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4.16Y</t>
+          <t>3.63Y+N</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.9798</t>
+          <t>1.9715</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8700</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司</t>
+          <t>南京高淳国有资产经营控股集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>D- 3.00</t>
+          <t>C- 10.84</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4216,16 +4226,20 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
+      <c r="U18" s="4" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>5.38</v>
+      </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>2.35%~2.45%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4236,23 +4250,23 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
+          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
+          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4267,20 +4281,24 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
+          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK18" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -4298,28 +4316,32 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP18" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4334,7 +4356,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4347,14 +4369,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ18" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ18" s="3"/>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26江津华信MTN001</t>
+          <t>26高教投资PPN002</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4364,47 +4384,47 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683462.IB</t>
+          <t>032690012.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.0</v>
+        <v>4.17</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.0</v>
+        <v>4.17</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>25江津华信MTN002A</t>
+          <t>26高教投资PPN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>3.93Y</t>
+          <t>56D</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.8922</t>
+          <t>1.6401</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4414,12 +4434,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司</t>
+          <t>泰州高教投资发展有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 20.51</t>
+          <t>C+ 34.41</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4443,46 +4463,46 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>5.63</v>
+        <v>2.4317</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.0</v>
+        <v>1.2</v>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>重庆市-江津区</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
+          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
+          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4497,24 +4517,20 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
+          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK19" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-09-01</t>
+        </is>
+      </c>
+      <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -4537,7 +4553,7 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
@@ -4547,12 +4563,12 @@
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
@@ -4585,62 +4601,62 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ19" s="3"/>
+      <c r="AZ19" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN002</t>
+          <t>26振兴Y2</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>132600024.IB</t>
+          <t>520449.SZ</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>2.5</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN001B</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>4.50Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.7922</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4650,12 +4666,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.57</t>
+          <t>C- 23.83</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4665,7 +4681,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4675,52 +4691,50 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="n">
-        <v>5.44</v>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>2.02%~2.12%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中国银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD20" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr">
+        <is>
+          <t>天府信用增进股份有限公司</t>
+        </is>
+      </c>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4730,68 +4744,64 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+      <c r="AP20" s="3"/>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4801,12 +4811,12 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
@@ -4824,55 +4834,55 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26宁波能源SCP002</t>
+          <t>26开滦Y1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>012682180.IB</t>
+          <t>245986.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H21" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1.99</v>
+      </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>GC甬能Y1</t>
+          <t>25开滦MTN001(科创票据)</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>3.51Y+N</t>
+          <t>1.38Y+2.00Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.8509</t>
+          <t>1.8119</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4882,12 +4892,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司</t>
+          <t>开滦(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 18.20</t>
+          <t>C 29.64</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4897,7 +4907,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4907,50 +4917,46 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.64%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD21" s="3" t="inlineStr">
-        <is>
-          <t>宁波开发投资集团有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4960,12 +4966,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券</t>
+          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4975,25 +4981,29 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2027-03-30</t>
-        </is>
-      </c>
-      <c r="AK21" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK21" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -5001,27 +5011,27 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5031,12 +5041,12 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
@@ -5049,14 +5059,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ21" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ21" s="3"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26太湖新城MTN010</t>
+          <t>26宁波能源SCP002(取消发行)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5066,47 +5074,43 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>102683461.IB</t>
+          <t>DY012682180.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>1.98</v>
-      </c>
+          <t>1.40 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26太新Y3</t>
+          <t>GC甬能Y1</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>4.93Y+N</t>
+          <t>3.51Y+N</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.8931</t>
+          <t>1.8509</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5116,12 +5120,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
+          <t>宁波能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 40.72</t>
+          <t>C- 18.20</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5144,47 +5148,47 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U22" s="4" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>1.92</v>
-      </c>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.60%~1.64%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
+          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD22" s="3"/>
+          <t>宁波银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr">
+        <is>
+          <t>宁波开发投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5199,7 +5203,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
+          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券(取消发行)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5209,7 +5213,7 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2027-03-30</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
@@ -5230,32 +5234,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5265,12 +5269,12 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW22" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX22" s="3" t="inlineStr">
@@ -5283,7 +5287,9 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ22" s="3"/>
+      <c r="AZ22" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
@@ -5353,7 +5359,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C 25.48</t>
+          <t>C 29.07</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5589,7 +5595,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 36.99</t>
+          <t>C+ 34.45</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -6051,7 +6057,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>B- 39.39</t>
+          <t>B- 38.13</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6283,7 +6289,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B- 44.10</t>
+          <t>B- 45.00</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6450,7 +6456,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26江宁滨江PPN002</t>
+          <t>26无锡城南PPN001(取消发行)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6461,40 +6467,30 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>1.73</v>
-      </c>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>25江宁滨江PPN004</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>2.18Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.8442</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6504,12 +6500,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司</t>
+          <t>无锡市城南建设投资发展有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C 25.72</t>
+          <t>C- 24.04</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6532,41 +6528,33 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U28" s="4" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t>1.88%~1.98%</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X28" s="3"/>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
+          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6587,7 +6575,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
+          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6597,7 +6585,7 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
@@ -6623,7 +6611,7 @@
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>8*无效</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
@@ -6633,12 +6621,12 @@
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
@@ -6676,182 +6664,208 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26无锡城南PPN001(取消发行)</t>
+          <t>26光大01</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
-        </is>
-      </c>
-      <c r="C29" s="3"/>
+          <t>08-31 19:00</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>524991.SZ</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.6</v>
+        <v>20.0</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H29" s="3"/>
+          <t>1.10 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1.55</v>
+      </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>24光大集团MTN004A</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>2.84Y</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>1.6671</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>1.6800/--</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>中国光大集团股份公司</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>B- 38.65</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>08-31 15:00</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>无锡市城南建设投资发展有限公司</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>C+ 32.48</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>08-31 09:00</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X29" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z29" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
+          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
+          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM29" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6884,70 +6898,70 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26光大01</t>
+          <t>26郴新01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>524991.SZ</t>
+          <t>283833.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>20.0</v>
+        <v>2.78</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>24光大集团MTN004A</t>
+          <t>24郴新02</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>3.14Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6671</t>
+          <t>2.2500</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司</t>
+          <t>郴州市新天投资有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 39.61</t>
+          <t>C+ 33.49</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6957,7 +6971,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6974,37 +6988,33 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.40%~2.50%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z30" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖南省-郴州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -7015,34 +7025,30 @@
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
+          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7060,32 +7066,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7118,7 +7124,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26开滦Y1</t>
+          <t>26金霞01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7128,45 +7134,47 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>245986.SH</t>
+          <t>283880.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F31" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>25开滦MTN001(科创票据)</t>
+          <t>25金霞01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1.38Y+2.00Y</t>
+          <t>4.13Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.8119</t>
+          <t>1.9567</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7176,12 +7184,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司</t>
+          <t>湖南金霞发展集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C 29.29</t>
+          <t>C- 10.34</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7201,10 +7209,12 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U31" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>5.85</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
@@ -7213,28 +7223,28 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
+          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -7255,24 +7265,20 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="AK31" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7280,17 +7286,17 @@
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
@@ -7300,27 +7306,27 @@
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -7348,70 +7354,72 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26郴新01</t>
+          <t>26淮安国投MTN005</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:30</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>283833.SH</t>
+          <t>102683459.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F32" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.30 ~ 2.10</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>24郴新02</t>
+          <t>25淮安国投MTN003</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>3.14Y</t>
+          <t>1.66Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2.2500</t>
+          <t>1.6367</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6000</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.49</t>
+          <t>C- 18.99</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7421,7 +7429,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7431,46 +7439,50 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>2.40%~2.50%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>湖南省-郴州市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
+          <t>本期发行金额2亿元,本次中期票据募集资金拟全部用于偿还发行人到期债券。[23 淮安国投MTN004]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司</t>
+          <t>徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7480,28 +7492,28 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
@@ -7511,7 +7523,7 @@
       </c>
       <c r="AN32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO32" s="3" t="inlineStr">
@@ -7521,7 +7533,7 @@
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
@@ -7574,55 +7586,57 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y2</t>
+          <t>26江津华信MTN001</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>520449.SZ</t>
+          <t>102683462.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
         <v>3.0</v>
       </c>
-      <c r="F33" s="3"/>
+      <c r="F33" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.28</v>
+        <v>1.78</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>25江津华信MTN002A</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>3.93Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.8922</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7632,12 +7646,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>C- 20.23</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7647,7 +7661,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7657,19 +7671,23 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>5.6333</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>2.02%~2.12%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7680,27 +7698,23 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>重庆市-江津区</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3" t="inlineStr">
-        <is>
-          <t>天府信用增进股份有限公司</t>
-        </is>
-      </c>
+          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7710,79 +7724,87 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP33" s="3"/>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7795,134 +7817,144 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ33" s="3"/>
+      <c r="AZ33" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26金霞01</t>
+          <t>26广州净水GN002</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>283880.SH</t>
+          <t>132600024.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>26广州净水GN001B</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>4.50Y</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1.7922</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>广州市净水有限公司</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>D+ 7.27</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>08-31 09:00</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>25金霞01</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>4.13Y</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>1.9567</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>湖南金霞发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t>C- 11.49</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t>08-31 15:00</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U34" s="3"/>
+      <c r="U34" s="4" t="n">
+        <v>5.44</v>
+      </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z34" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
+          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
+          <t>广发证券股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -7932,17 +7964,17 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
@@ -7953,54 +7985,54 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO34" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR34" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8008,7 +8040,7 @@
       </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX34" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-31.xlsx
+++ b/data/credit_bond_all_2026-08-31.xlsx
@@ -1643,7 +1643,9 @@
           <t>1.70 ~ 2.10</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.85</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -3448,7 +3450,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN003(资产担保)</t>
+          <t>26盐城创投PPN001(混合型科创债)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3458,47 +3460,47 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683428.IB</t>
+          <t>032680495.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.79</t>
+          <t>2.15 ~ 3.05</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.79</v>
+        <v>2.38</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN002</t>
+          <t>25盐创K1</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>2.86Y</t>
+          <t>4.16Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.7832</t>
+          <t>1.9798</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3508,12 +3510,12 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司</t>
+          <t>盐城市创新创业投资有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 18.84</t>
+          <t>D- 1.50</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3540,36 +3542,36 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X15" s="3"/>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>2.35%~2.45%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币，用于偿还金融机构借款</t>
+          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>温州交运集团房地产投资开发有限公司</t>
-        </is>
-      </c>
+          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
           <t>定向工具(PPN)</t>
@@ -3587,24 +3589,20 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
+          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK15" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3612,7 +3610,7 @@
       </c>
       <c r="AM15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN15" s="3" t="inlineStr">
@@ -3622,32 +3620,28 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP15" s="3"/>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3657,7 +3651,7 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW15" s="3" t="inlineStr">
@@ -3675,12 +3669,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ15" s="3"/>
+      <c r="AZ15" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26盐城创投PPN001(混合型科创债)</t>
+          <t>26太湖新城MTN010</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3690,47 +3686,47 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>032680495.IB</t>
+          <t>102683461.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2.15 ~ 3.05</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>25盐创K1</t>
+          <t>26太新Y3</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.16Y</t>
+          <t>4.93Y+N</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.9798</t>
+          <t>1.8931</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3740,12 +3736,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司</t>
+          <t>无锡市太湖新城发展集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>D- 1.50</t>
+          <t>B- 35.06</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3768,43 +3764,47 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>1.92</v>
+      </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>2.35%~2.45%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
+          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
+          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
+          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="AM16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN16" s="3" t="inlineStr">
@@ -3850,28 +3850,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP16" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3886,7 +3890,7 @@
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3899,14 +3903,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ16" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ16" s="3"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26太湖新城MTN010</t>
+          <t>26高淳国资MTN001</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3916,62 +3918,62 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683461.IB</t>
+          <t>102690020.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26太新Y3</t>
+          <t>25高淳国资MTN002</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.93Y+N</t>
+          <t>3.63Y+N</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.8931</t>
+          <t>1.9715</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8700</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
+          <t>南京高淳国有资产经营控股集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 35.06</t>
+          <t>C- 10.84</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3995,40 +3997,40 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.89</v>
+        <v>5.05</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.92</v>
+        <v>5.38</v>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
+          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
+          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4049,7 +4051,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
+          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4059,10 +4061,14 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK17" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL17" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -4070,7 +4076,7 @@
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4085,27 +4091,27 @@
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4138,7 +4144,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26高淳国资MTN001</t>
+          <t>26高教投资PPN002</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4148,62 +4154,62 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102690020.IB</t>
+          <t>032690012.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.0</v>
+        <v>4.17</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.0</v>
+        <v>4.17</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25高淳国资MTN002</t>
+          <t>26高教投资PPN001</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.63Y+N</t>
+          <t>56D</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.9715</t>
+          <t>1.6401</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/1.8700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司</t>
+          <t>泰州高教投资发展有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 10.84</t>
+          <t>C+ 34.41</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4227,14 +4233,14 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>5.05</v>
+        <v>2.4317</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>5.38</v>
+        <v>1.2</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
@@ -4244,29 +4250,29 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
+          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
+          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4281,24 +4287,20 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
+          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-09-01</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -4306,7 +4308,7 @@
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
@@ -4316,32 +4318,32 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4356,7 +4358,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4369,62 +4371,62 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ18" s="3"/>
+      <c r="AZ18" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN002</t>
+          <t>26振兴Y2</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>032690012.IB</t>
+          <t>520449.SZ</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>4.17</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN001</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>56D</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.6401</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4434,12 +4436,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.41</t>
+          <t>C- 23.83</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4449,7 +4451,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4459,50 +4461,50 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U19" s="4" t="n">
-        <v>2.4317</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>1.2</v>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>2.02%~2.12%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD19" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr">
+        <is>
+          <t>天府信用增进股份有限公司</t>
+        </is>
+      </c>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4512,12 +4514,12 @@
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4527,53 +4529,49 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM19" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP19" s="3"/>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4583,12 +4581,12 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
@@ -4601,14 +4599,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ19" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ19" s="3"/>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y2</t>
+          <t>26开滦Y1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4618,45 +4614,45 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>520449.SZ</t>
+          <t>245986.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>25开滦MTN001(科创票据)</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>1.38Y+2.00Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.8119</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4666,12 +4662,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>开滦(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>C 29.64</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4698,40 +4694,36 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>2.02%~2.12%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD20" s="3" t="inlineStr">
-        <is>
-          <t>天府信用增进股份有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4744,25 +4736,29 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK20" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK20" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4770,7 +4766,7 @@
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
@@ -4783,25 +4779,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP20" s="3"/>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>金属非金属新材料</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW20" s="3" t="inlineStr">
@@ -4834,55 +4834,53 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26开滦Y1</t>
+          <t>26宁波能源SCP002(取消发行)</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>245986.SH</t>
+          <t>DY012682180.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>1.99</v>
-      </c>
+          <t>1.40 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>25开滦MTN001(科创票据)</t>
+          <t>GC甬能Y1</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>1.38Y+2.00Y</t>
+          <t>3.51Y+N</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.8119</t>
+          <t>1.8509</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4892,12 +4890,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司</t>
+          <t>宁波能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C 29.64</t>
+          <t>C- 18.20</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4907,7 +4905,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4917,46 +4915,50 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.60%~1.64%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
+          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD21" s="3"/>
+          <t>宁波银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>宁波开发投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4966,12 +4968,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券(取消发行)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4981,90 +4983,88 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="AK21" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-03-30</t>
+        </is>
+      </c>
+      <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY21" s="3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO21" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ21" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR21" s="3" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>煤炭开采</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW21" s="3" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AX21" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26宁波能源SCP002(取消发行)</t>
+          <t>26青城租赁MTN003</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5074,43 +5074,47 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>DY012682180.IB</t>
+          <t>102690021.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>2.1</v>
+      </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>GC甬能Y1</t>
+          <t>26青城租赁MTN002</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>3.51Y+N</t>
+          <t>2.61Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.8509</t>
+          <t>2.1005</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5120,12 +5124,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司</t>
+          <t>青岛城乡建设融资租赁有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 18.20</t>
+          <t>C 29.07</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5135,7 +5139,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 14:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5148,47 +5152,47 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.64%</t>
+          <t>2.31%~2.41%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
+          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD22" s="3" t="inlineStr">
-        <is>
-          <t>宁波开发投资集团有限公司</t>
-        </is>
-      </c>
+          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5203,7 +5207,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券(取消发行)</t>
+          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5213,10 +5217,14 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2027-03-30</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5234,7 +5242,7 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
@@ -5244,22 +5252,22 @@
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5269,7 +5277,7 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW22" s="3" t="inlineStr">
@@ -5287,14 +5295,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ22" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ22" s="3"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN003</t>
+          <t>26立讯精工SCP006</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5304,62 +5310,62 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102690021.IB</t>
+          <t>012682178.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.20 ~ 1.49</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN002</t>
+          <t>26立讯精工SCP001(科创债)</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.61Y</t>
+          <t>53D</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2.1005</t>
+          <t>1.5142</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5000</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C 29.07</t>
+          <t>C+ 34.45</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5369,7 +5375,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>08-31 14:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5383,19 +5389,17 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>0.92</v>
+      </c>
+      <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2.31%~2.41%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5406,28 +5410,28 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
+          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
+          <t>杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
@@ -5437,7 +5441,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
+          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5447,14 +5451,10 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK23" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5472,32 +5472,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5530,7 +5530,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP006</t>
+          <t>26新和成股MTN002(科创债)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>012682178.IB</t>
+          <t>102683464.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -5556,46 +5556,46 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.49</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP001(科创债)</t>
+          <t>26新和成股SCP001(科创债)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>53D</t>
+          <t>60D</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.5142</t>
+          <t>1.5159</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>浙江新和成股份有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.45</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5619,44 +5619,42 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="V24" s="3"/>
+        <v>1.59</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>1.17</v>
+      </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
+      <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
+          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5671,7 +5669,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
+          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5681,10 +5679,14 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AK24" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK24" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5707,27 +5709,27 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>化学制药</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5760,7 +5762,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26新和成股MTN002(科创债)</t>
+          <t>26华能新能SCP010</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5770,62 +5772,62 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>102683464.IB</t>
+          <t>012682177.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>1.35 ~ 1.55</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26新和成股SCP001(科创债)</t>
+          <t>26华能新能SCP009</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>60D</t>
+          <t>50D</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.5159</t>
+          <t>1.4780</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司</t>
+          <t>华能新能源股份有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 38.13</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5849,47 +5851,51 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.59</v>
+        <v>4.8</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.17</v>
+        <v>1.0</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
-        </is>
-      </c>
-      <c r="Y25" s="3"/>
+          <t>1.45%~1.49%</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
+          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5899,7 +5905,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
+          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5909,14 +5915,10 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5939,27 +5941,27 @@
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>化学制药</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5992,7 +5994,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP010</t>
+          <t>26苏交通CP005</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6002,12 +6004,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>012682177.IB</t>
+          <t>042680304.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>0.99Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -6018,46 +6020,46 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.37 ~ 1.67</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP009</t>
+          <t>26苏交通CP004</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>50D</t>
+          <t>354D</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.4780</t>
+          <t>1.5317</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.4900/--</t>
+          <t>1.5400/1.4293</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司</t>
+          <t>江苏交通控股有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>B- 38.13</t>
+          <t>B- 45.00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6081,19 +6083,19 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.8</v>
+        <v>2.985</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.0</v>
+        <v>1.25</v>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6104,28 +6106,28 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
+          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -6135,7 +6137,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
+          <t>江苏交通控股有限公司2026年度第五期短期融资券</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6145,7 +6147,7 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-08-27</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6166,32 +6168,32 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6224,7 +6226,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26苏交通CP005</t>
+          <t>26无锡城南PPN001(取消发行)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6232,64 +6234,48 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>042680304.IB</t>
-        </is>
-      </c>
+      <c r="C27" s="3"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>0.99Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>20.0</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.37 ~ 1.67</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>1.42</v>
-      </c>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>26苏交通CP004</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>354D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.4293</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司</t>
+          <t>无锡市城南建设投资发展有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B- 45.00</t>
+          <t>C- 24.04</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6312,47 +6298,39 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U27" s="4" t="n">
-        <v>2.985</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>1.25</v>
-      </c>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t>1.50%~1.54%</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X27" s="3"/>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
+          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,杭州银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6367,17 +6345,17 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司2026年度第五期短期融资券</t>
+          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2027-08-27</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
@@ -6398,12 +6376,12 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
@@ -6413,17 +6391,17 @@
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6456,182 +6434,208 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26无锡城南PPN001(取消发行)</t>
+          <t>26光大01</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
-        </is>
-      </c>
-      <c r="C28" s="3"/>
+          <t>08-31 19:00</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>524991.SZ</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.6</v>
+        <v>20.0</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H28" s="3"/>
+          <t>1.10 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1.55</v>
+      </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>24光大集团MTN004A</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>2.84Y</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>1.6671</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>1.6800/--</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>中国光大集团股份公司</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>B- 38.65</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>08-31 15:00</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>无锡市城南建设投资发展有限公司</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t>C- 24.04</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>08-31 09:00</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X28" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z28" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
+          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
+          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK28" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK28" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6664,70 +6668,70 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26光大01</t>
+          <t>26郴新01</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>524991.SZ</t>
+          <t>283833.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>20.0</v>
+        <v>2.78</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>24光大集团MTN004A</t>
+          <t>24郴新02</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>3.14Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.6671</t>
+          <t>2.2500</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司</t>
+          <t>郴州市新天投资有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>B- 38.65</t>
+          <t>C+ 33.49</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6737,7 +6741,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6754,37 +6758,33 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.40%~2.50%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖南省-郴州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6795,34 +6795,30 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
+          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="AK29" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6840,32 +6836,32 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6898,55 +6894,57 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26郴新01</t>
+          <t>26金霞01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:30</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>283833.SH</t>
+          <t>283880.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.33</v>
+        <v>1.79</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>24郴新02</t>
+          <t>25金霞01</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>3.14Y</t>
+          <t>4.13Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2.2500</t>
+          <t>1.9567</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -6956,12 +6954,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司</t>
+          <t>湖南金霞发展集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.49</t>
+          <t>C- 10.34</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6971,7 +6969,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6981,40 +6979,42 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U30" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>5.85</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>2.40%~2.50%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>湖南省-郴州市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司</t>
+          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AV30" s="3" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
@@ -7124,133 +7124,135 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26金霞01</t>
+          <t>26淮安国投MTN005</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>283880.SH</t>
+          <t>102683459.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.10</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>25淮安国投MTN003</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>1.66Y</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>1.6367</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>--/1.6000</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>淮安市国有联合投资发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>C- 18.99</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>08-31 09:00</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>25金霞01</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>4.13Y</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>1.9567</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>湖南金霞发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>C- 10.34</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>08-31 15:00</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="V31" s="3"/>
+        <v>6.05</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
+          <t>本期发行金额2亿元,本次中期票据募集资金拟全部用于偿还发行人到期债券。[23 淮安国投MTN004]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
+          <t>徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7260,75 +7262,75 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO31" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ31" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR31" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
       <c r="AV31" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7336,7 +7338,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7354,7 +7356,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN005</t>
+          <t>26江津华信MTN001</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7364,62 +7366,62 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>102683459.IB</t>
+          <t>102683462.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.10</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25淮安国投MTN003</t>
+          <t>25江津华信MTN002A</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>1.66Y</t>
+          <t>3.93Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6367</t>
+          <t>1.8922</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/1.6000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 18.99</t>
+          <t>C- 20.23</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7443,40 +7445,40 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>6.05</v>
+        <v>5.6333</v>
       </c>
       <c r="V32" s="4" t="n">
         <v>2.0</v>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>重庆市-江津区</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元,本次中期票据募集资金拟全部用于偿还发行人到期债券。[23 淮安国投MTN004]</t>
+          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司</t>
+          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7497,7 +7499,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年度第五期中期票据</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7507,10 +7509,14 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL32" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -7528,12 +7534,12 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
@@ -7581,12 +7587,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ32" s="3"/>
+      <c r="AZ32" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26江津华信MTN001</t>
+          <t>26广州净水GN002</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7596,47 +7604,47 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>102683462.IB</t>
+          <t>132600024.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.0</v>
+        <v>2.5</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.0</v>
+        <v>2.5</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>25江津华信MTN002A</t>
+          <t>26广州净水GN001B</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>3.93Y</t>
+          <t>4.50Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.8922</t>
+          <t>1.7922</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7646,12 +7654,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司</t>
+          <t>广州市净水有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 20.23</t>
+          <t>D+ 7.27</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7675,40 +7683,42 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>5.6333</v>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>5.44</v>
+      </c>
+      <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z33" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>重庆市-江津区</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
+          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
+          <t>广发证券股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7729,7 +7739,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
+          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7739,14 +7749,10 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK33" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -7764,32 +7770,32 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7817,14 +7823,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ33" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ33" s="3"/>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN002</t>
+          <t>26温州交运MTN003(资产担保)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7834,47 +7838,47 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>132600024.IB</t>
+          <t>102683428.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.5</v>
+        <v>1.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.5</v>
+        <v>1.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.50 ~ 1.79</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN001B</t>
+          <t>26温州交运MTN002</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>4.50Y</t>
+          <t>2.86Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.7922</t>
+          <t>1.7832</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7884,12 +7888,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司</t>
+          <t>温州市交通运输集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.27</t>
+          <t>C- 18.84</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7912,46 +7916,40 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U34" s="4" t="n">
-        <v>5.44</v>
-      </c>
+      <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t>1.74%~1.84%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X34" s="3"/>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
+          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币，用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中国银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3"/>
+          <t>浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr">
+        <is>
+          <t>温州交运集团房地产投资开发有限公司</t>
+        </is>
+      </c>
       <c r="AE34" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -7969,7 +7967,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
+          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7979,10 +7977,14 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK34" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK34" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -8005,27 +8007,27 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>非盈利性交运服务</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>非盈利性交运服务</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8035,7 +8037,7 @@
       </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-31.xlsx
+++ b/data/credit_bond_all_2026-08-31.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-02" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-03" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26知识城SCP002</t>
+          <t>26赣出版SCP004(取消发行)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,62 +702,58 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>012682176.IB</t>
+          <t>DY012682179.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.27Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.52</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1.42</v>
-      </c>
+          <t>1.33 ~ 1.53</t>
+        </is>
+      </c>
+      <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>26知识城SCP001</t>
+          <t>25赣出版MTN001</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>122D</t>
+          <t>215D+1.00Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.5318</t>
+          <t>1.5317</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.5000</t>
+          <t>1.5600/1.5300</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>知识城(广州)投资集团有限公司</t>
+          <t>江西省出版传媒集团有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 40.67</t>
+          <t>C- 15.42</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -780,20 +776,16 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U3" s="4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>1.0</v>
-      </c>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -804,17 +796,17 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行规模0亿元,发行金额上限10亿元(含),用于偿还债务融资工具[25知识城SCP007]</t>
+          <t>本期超短期融资券募集资金5亿元，拟用于偿还有息债务[26赣出版SCP002]</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,渤海银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD3" s="3"/>
@@ -835,7 +827,7 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>知识城(广州)投资集团有限公司2026年度第二期超短期融资券</t>
+          <t>江西省出版传媒集团有限公司2026年度第四期超短期融资券(取消发行)</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -845,10 +837,14 @@
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="AK3" s="3"/>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -866,32 +862,32 @@
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>传媒</t>
         </is>
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>出版</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>出版</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU3" s="3" t="inlineStr">
@@ -919,29 +915,27 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ3" s="4" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="AZ3" s="3"/>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26赣出版SCP004(取消发行)</t>
+          <t>26厦门产投MTN003(科创债)(取消发行)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>DY012682179.IB</t>
+          <t>DY102683466.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -950,44 +944,44 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.33 ~ 1.53</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>25赣出版MTN001</t>
+          <t>26厦门产投MTN002(科创债)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>215D+1.00Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>1.9088</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.5600/1.5300</t>
+          <t>1.8950/1.8800</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>江西省出版传媒集团有限公司</t>
+          <t>厦门市产业投资有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 19.17</t>
+          <t>A 75.38</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -997,7 +991,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 11:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1007,19 +1001,19 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1027,26 +1021,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z4" s="3"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元，拟用于偿还有息债务[26赣出版SCP002]</t>
+          <t>本期科技创新债券发行金额为5亿元,本期发行的募集资金扣除承销费后,拟全部用于置换发行人本期科技创新债券发行之日起一年以内用于科技创新领域股权投资或基金出资的自有资金投入。</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1061,7 +1059,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>江西省出版传媒集团有限公司2026年度第四期超短期融资券(取消发行)</t>
+          <t>厦门市产业投资有限公司2026年度第三期科技创新债券(取消发行)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1071,82 +1069,74 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP4" s="3"/>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY4" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>传媒</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>出版</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>出版</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>贸易</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ4" s="3"/>
@@ -1154,70 +1144,74 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN003(科创债)</t>
+          <t>26越秀集团MTN004(绿色)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>08-31 11:30</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>102683466.IB</t>
+          <t>102683458.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+          <t>1.94 ~ 2.35</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>66.17</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN002(科创债)</t>
+          <t>26广越12</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>9.98Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.9088</t>
+          <t>2.3356</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1.8950/1.8800</t>
+          <t>2.3500/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司</t>
+          <t>广州越秀集团股份有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>A 71.63</t>
+          <t>C+ 30.93</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1227,7 +1221,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>08-31 11:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1237,19 +1231,21 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U5" s="3"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>1.15</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>2.24%~2.34%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1257,24 +1253,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行金额为5亿元,本期发行的募集资金扣除承销费后,拟全部用于置换发行人本期科技创新债券发行之日起一年以内用于科技创新领域股权投资或基金出资的自有资金投入。</t>
+          <t>发行人拟将本期绿色中期票据募集资金6亿元用于偿还发行人有息债务[21越秀集团GN002（革命老区）]</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
+          <t>中国银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
@@ -1295,7 +1287,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
+          <t>广州越秀集团股份有限公司2026年度第四期绿色中期票据</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1305,13 +1297,17 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK5" s="3"/>
+          <t>2036-08-31</t>
+        </is>
+      </c>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
@@ -1321,33 +1317,37 @@
       </c>
       <c r="AN5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP5" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AY5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ5" s="3"/>
@@ -1380,72 +1380,74 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN004(绿色)</t>
+          <t>26晋能电力GN005(碳中和债)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>08-31 11:30</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>102683458.IB</t>
+          <t>132680093.IB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.94 ~ 2.35</t>
+          <t>1.70 ~ 2.10</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="I6" s="3"/>
+        <v>1.85</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>44.96</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26广越12</t>
+          <t>25晋能电力MTN002</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>9.98Y</t>
+          <t>5.38Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>2.3356</t>
+          <t>1.9709</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>2.3500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司</t>
+          <t>晋能控股电力集团有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.55</t>
+          <t>C+ 33.22</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1465,21 +1467,19 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>1.15</v>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>2.24%~2.34%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1490,17 +1490,17 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>山西省-太原市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期绿色中期票据募集资金6亿元用于偿还发行人有息债务[21越秀集团GN002（革命老区）]</t>
+          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中信银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第四期绿色中期票据</t>
+          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
@@ -1531,82 +1531,78 @@
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2036-08-31</t>
-        </is>
-      </c>
-      <c r="AK6" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY6" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AM6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AO6" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ6" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR6" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ6" s="3"/>
@@ -1614,17 +1610,17 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26晋能电力GN005(碳中和债)</t>
+          <t>26ZTTZK1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>132680093.IB</t>
+          <t>246000.SH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1633,53 +1629,55 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I7" s="3"/>
+        <v>1.81</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>39.94</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>25晋能电力MTN002</t>
+          <t>25ZTTZK1</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>5.38Y</t>
+          <t>3.97Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.9709</t>
+          <t>1.7685</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8300</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司</t>
+          <t>中铁投资集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 36.86</t>
+          <t>D 4.00</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1689,7 +1687,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1702,7 +1700,9 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>3.75</v>
+      </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1719,41 +1719,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z7" s="3"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>山西省-太原市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将10亿元用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG7" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
+          <t>中铁投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1769,7 +1773,7 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AM7" s="3" t="inlineStr">
@@ -1789,27 +1793,27 @@
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1834,7 +1838,7 @@
       </c>
       <c r="AY7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ7" s="3"/>
@@ -1842,7 +1846,7 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26ZTTZK1</t>
+          <t>26光大02(取消发行)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1852,7 +1856,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>246000.SH</t>
+          <t>DY524992.SZ</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1861,51 +1865,49 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>1.81</v>
-      </c>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>25ZTTZK1</t>
+          <t>21光大集团MTN001B</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>3.97Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.7685</t>
+          <t>1.7413</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/1.8300</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>中铁投资集团有限公司</t>
+          <t>中国光大集团股份公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.33</t>
+          <t>B- 37.31</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1915,7 +1917,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1932,12 +1934,12 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1957,12 +1959,12 @@
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将10亿元用于偿还有息负债</t>
+          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
+          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
@@ -1973,17 +1975,17 @@
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>中铁投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -2014,32 +2016,32 @@
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2072,100 +2074,108 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26光大02(取消发行)</t>
+          <t>26沪盛K1</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>DY524992.SZ</t>
+          <t>245999.SH</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>29.17</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>26国盛MTN003(科创债)</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>9.88Y</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>2.0875</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>--/2.0700</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>上海国盛(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>C- 24.21</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>08-31 16:00</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>21光大集团MTN001B</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>4.95Y</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>1.7413</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>1.7600/--</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>中国光大集团股份公司</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>B- 38.65</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>08-31 15:00</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U9" s="3"/>
+      <c r="U9" s="4" t="n">
+        <v>3.93</v>
+      </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2173,24 +2183,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
@@ -2201,17 +2207,17 @@
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)(取消发行)</t>
+          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2221,7 +2227,7 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2036-09-02</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
@@ -2242,27 +2248,27 @@
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
@@ -2300,70 +2306,74 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26沪盛K1</t>
+          <t>26宁沪高MTN002</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:30</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>245999.SH</t>
+          <t>102683460.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I10" s="3"/>
+        <v>1.54</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>28.24</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26国盛MTN003(科创债)</t>
+          <t>26宁沪高MTN001</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>9.88Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>2.0875</t>
+          <t>1.6734</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/2.0700</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司</t>
+          <t>江苏宁沪高速公路股份有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C 29.01</t>
+          <t>C 26.94</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2373,7 +2383,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2383,13 +2393,15 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V10" s="3"/>
+        <v>4.66</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -2397,7 +2409,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2408,23 +2420,23 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
+          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2434,12 +2446,12 @@
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2449,13 +2461,17 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2036-09-02</t>
-        </is>
-      </c>
-      <c r="AK10" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK10" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL10" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM10" s="3" t="inlineStr">
@@ -2465,7 +2481,7 @@
       </c>
       <c r="AN10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO10" s="3" t="inlineStr">
@@ -2475,27 +2491,27 @@
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2528,17 +2544,17 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y3</t>
+          <t>26太湖新城MTN010</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>520450.SZ</t>
+          <t>102683461.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -2547,36 +2563,40 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 3.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="I11" s="3"/>
+        <v>1.98</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>56.94</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>26太新Y3</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>4.93Y+N</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.8931</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2586,12 +2606,12 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>无锡市太湖新城发展集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>B- 36.75</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2601,7 +2621,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2611,50 +2631,50 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>1.92</v>
+      </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>成都中小企业融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2664,74 +2684,78 @@
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
+          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO11" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP11" s="3"/>
-      <c r="AQ11" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR11" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS11" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
@@ -2754,70 +2778,74 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y1</t>
+          <t>26高淳国资MTN001</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>520448.SZ</t>
+          <t>102690020.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="I12" s="3"/>
+        <v>1.85</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>59.24</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>25高淳国资MTN002</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>3.63Y+N</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.9715</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8700</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>南京高淳国有资产经营控股集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>C- 14.34</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2827,7 +2855,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2837,19 +2865,23 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>5.38</v>
+      </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2860,27 +2892,23 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>重庆三峡融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2890,74 +2918,82 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
+          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK12" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK12" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP12" s="3"/>
-      <c r="AQ12" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
@@ -2980,7 +3016,7 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN002</t>
+          <t>26高教投资PPN002</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2990,62 +3026,64 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>102683460.IB</t>
+          <t>032690012.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.0</v>
+        <v>4.17</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.0</v>
+        <v>4.17</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I13" s="3"/>
+        <v>1.8</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>54.76</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN001</t>
+          <t>26高教投资PPN001</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.78Y</t>
+          <t>56D</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.6734</t>
+          <t>1.6401</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司</t>
+          <t>泰州高教投资发展有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.91</t>
+          <t>B- 40.98</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3069,46 +3107,46 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>4.66</v>
+        <v>2.4317</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
+          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司</t>
+          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3123,24 +3161,20 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
+          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK13" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-09-01</t>
+        </is>
+      </c>
+      <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3158,12 +3192,12 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
@@ -3173,17 +3207,17 @@
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3211,62 +3245,66 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ13" s="3"/>
+      <c r="AZ13" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26江宁滨江PPN002</t>
+          <t>26开滦Y1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>032680505.IB</t>
+          <t>245986.SH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.3</v>
+        <v>10.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.3</v>
+        <v>10.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="I14" s="3"/>
+        <v>1.99</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>73.24</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25江宁滨江PPN004</t>
+          <t>25开滦MTN001(科创票据)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2.18Y</t>
+          <t>1.38Y+2.00Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.8442</t>
+          <t>1.8119</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3276,12 +3314,12 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司</t>
+          <t>开滦(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 24.12</t>
+          <t>C- 24.06</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3291,7 +3329,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3301,15 +3339,13 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>4.03</v>
+      </c>
+      <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
           <t>6-</t>
@@ -3317,34 +3353,34 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3354,68 +3390,72 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
+          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
-        </is>
-      </c>
-      <c r="AK14" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK14" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>8*无效</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3430,7 +3470,7 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
@@ -3443,14 +3483,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ14" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ14" s="3"/>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26盐城创投PPN001(混合型科创债)</t>
+          <t>26知识城SCP002</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3460,62 +3498,64 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>032680495.IB</t>
+          <t>012682176.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.27Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2.15 ~ 3.05</t>
+          <t>1.30 ~ 1.52</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="I15" s="3"/>
+        <v>1.42</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>16.88</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25盐创K1</t>
+          <t>26知识城SCP001</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.16Y</t>
+          <t>122D</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.9798</t>
+          <t>1.5318</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.5000</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司</t>
+          <t>知识城(广州)投资集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>D- 1.50</t>
+          <t>B- 42.68</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3538,43 +3578,47 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
+      <c r="U15" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>2.35%~2.45%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
+          <t>本期超短期融资券基础发行规模0亿元,发行金额上限10亿元(含),用于偿还债务融资工具[25知识城SCP007]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
+          <t>浙商银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3589,17 +3633,17 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
+          <t>知识城(广州)投资集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
@@ -3610,7 +3654,7 @@
       </c>
       <c r="AM15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN15" s="3" t="inlineStr">
@@ -3620,23 +3664,27 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP15" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
@@ -3670,23 +3718,23 @@
         </is>
       </c>
       <c r="AZ15" s="4" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26太湖新城MTN010</t>
+          <t>26振兴Y1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683461.IB</t>
+          <t>520448.SZ</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3695,38 +3743,40 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10.0</v>
+        <v>2.5</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.0</v>
+        <v>2.5</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I16" s="3"/>
+        <v>2.28</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>86.94</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26太新Y3</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.93Y+N</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.8931</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3736,12 +3786,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B- 35.06</t>
+          <t>C- 15.54</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3751,7 +3801,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3761,50 +3811,52 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>1.92</v>
-      </c>
+        <v>3.14</v>
+      </c>
+      <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>重庆三峡融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3814,68 +3866,64 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP16" s="3"/>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3885,7 +3933,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3908,7 +3956,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26高淳国资MTN001</t>
+          <t>26江宁滨江PPN002</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3918,19 +3966,19 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102690020.IB</t>
+          <t>032680505.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.0</v>
+        <v>2.3</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.0</v>
+        <v>2.3</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -3938,42 +3986,44 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I17" s="3"/>
+        <v>1.73</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>47.76</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25高淳国资MTN002</t>
+          <t>25江宁滨江PPN004</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>3.63Y+N</t>
+          <t>2.18Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.9715</t>
+          <t>1.8442</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/1.8700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司</t>
+          <t>南京江宁滨江新城开发建设有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 10.84</t>
+          <t>C 25.68</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3997,14 +4047,14 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>5.05</v>
+        <v>4.5217</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>5.38</v>
+        <v>1.5</v>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
@@ -4014,7 +4064,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
@@ -4025,18 +4075,18 @@
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
+          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
+          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4051,24 +4101,20 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
+          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK17" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-09-01</t>
+        </is>
+      </c>
+      <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -4076,7 +4122,7 @@
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4091,27 +4137,27 @@
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8*无效</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4126,7 +4172,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4139,12 +4185,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ17" s="3"/>
+      <c r="AZ17" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN002</t>
+          <t>26盐城创投PPN001(混合型科创债)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4154,47 +4202,49 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>032690012.IB</t>
+          <t>032680495.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.17</v>
+        <v>2.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.17</v>
+        <v>2.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>2.15 ~ 3.05</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I18" s="3"/>
+        <v>2.38</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>96.94</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN001</t>
+          <t>25盐创K1</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>56D</t>
+          <t>4.16Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.6401</t>
+          <t>1.9798</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -4204,12 +4254,12 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司</t>
+          <t>盐城市创新创业投资有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.41</t>
+          <t>C- 14.00</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4233,40 +4283,38 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.4317</v>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>1.85</v>
+      </c>
+      <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>2.35%~2.45%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
+          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4287,7 +4335,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
+          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4297,7 +4345,7 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
@@ -4308,7 +4356,7 @@
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
@@ -4318,32 +4366,28 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP18" s="3"/>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4372,61 +4416,65 @@
         </is>
       </c>
       <c r="AZ18" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y2</t>
+          <t>26郴新01</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>520449.SZ</t>
+          <t>283833.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F19" s="3"/>
+        <v>2.78</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>2.78</v>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="I19" s="3"/>
+        <v>2.33</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>91.94</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>24郴新02</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>3.14Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>2.2500</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4436,12 +4484,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>郴州市新天投资有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 23.83</t>
+          <t>C+ 31.72</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4451,7 +4499,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4464,44 +4512,42 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U19" s="3"/>
+      <c r="U19" s="4" t="n">
+        <v>3.79</v>
+      </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>2.02%~2.12%</t>
+          <t>2.40%~2.50%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>湖南省-郴州市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD19" s="3" t="inlineStr">
-        <is>
-          <t>天府信用增进股份有限公司</t>
-        </is>
-      </c>
+          <t>财信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4514,12 +4560,12 @@
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4550,28 +4596,32 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP19" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>金属非金属新材料</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4581,12 +4631,12 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
@@ -4604,55 +4654,53 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26开滦Y1</t>
+          <t>26宁波能源SCP002(取消发行)</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>245986.SH</t>
+          <t>DY012682180.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>1.99</v>
-      </c>
+          <t>1.40 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>25开滦MTN001(科创票据)</t>
+          <t>GC甬能Y1</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.38Y+2.00Y</t>
+          <t>3.51Y+N</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.8119</t>
+          <t>1.8509</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4662,12 +4710,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司</t>
+          <t>宁波能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C 29.64</t>
+          <t>C- 18.20</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4677,7 +4725,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4687,46 +4735,50 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.60%~1.64%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
+          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD20" s="3"/>
+          <t>宁波银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr">
+        <is>
+          <t>宁波开发投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4736,12 +4788,12 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券(取消发行)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4751,90 +4803,88 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="AK20" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-03-30</t>
+        </is>
+      </c>
+      <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM20" s="3" t="inlineStr">
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY20" s="3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO20" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ20" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR20" s="3" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>煤炭开采</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW20" s="3" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AX20" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AZ20" s="3"/>
+      <c r="AZ20" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26宁波能源SCP002(取消发行)</t>
+          <t>26青城租赁MTN003</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4844,43 +4894,49 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>DY012682180.IB</t>
+          <t>102690021.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>84.24</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>GC甬能Y1</t>
+          <t>26青城租赁MTN002</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>3.51Y+N</t>
+          <t>2.61Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.8509</t>
+          <t>2.1005</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4890,12 +4946,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司</t>
+          <t>青岛城乡建设融资租赁有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 18.20</t>
+          <t>C+ 32.77</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4905,7 +4961,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 14:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4918,47 +4974,47 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
+      <c r="U21" s="4" t="n">
+        <v>2.7667</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.64%</t>
+          <t>2.31%~2.41%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
+          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD21" s="3" t="inlineStr">
-        <is>
-          <t>宁波开发投资集团有限公司</t>
-        </is>
-      </c>
+          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4973,7 +5029,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券(取消发行)</t>
+          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4983,10 +5039,14 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2027-03-30</t>
-        </is>
-      </c>
-      <c r="AK21" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK21" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5004,7 +5064,7 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
@@ -5014,22 +5074,22 @@
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5039,7 +5099,7 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW21" s="3" t="inlineStr">
@@ -5057,14 +5117,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ21" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ21" s="3"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN003</t>
+          <t>26立讯精工SCP006</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5074,62 +5132,64 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>102690021.IB</t>
+          <t>012682178.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.20 ~ 1.49</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I22" s="3"/>
+        <v>1.49</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>31.81</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN002</t>
+          <t>26立讯精工SCP001(科创债)</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.61Y</t>
+          <t>53D</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2.1005</t>
+          <t>1.5142</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5000</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C 29.07</t>
+          <t>B- 38.22</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5139,7 +5199,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>08-31 14:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5153,19 +5213,17 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>0.92</v>
+      </c>
+      <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>2.31%~2.41%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5176,28 +5234,28 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
+          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
+          <t>杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -5207,7 +5265,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
+          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5217,14 +5275,10 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK22" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5242,32 +5296,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5300,7 +5354,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP006</t>
+          <t>26新和成股MTN002(科创债)</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5310,12 +5364,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>012682178.IB</t>
+          <t>102683464.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -5326,46 +5380,48 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.49</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I23" s="3"/>
+        <v>1.6</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>34.24</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP001(科创债)</t>
+          <t>26新和成股SCP001(科创债)</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>53D</t>
+          <t>60D</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.5142</t>
+          <t>1.5159</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>浙江新和成股份有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.45</t>
+          <t>C- 21.00</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5389,44 +5445,42 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="V23" s="3"/>
+        <v>1.59</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.17</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
-        </is>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
+      <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
+          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5441,7 +5495,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
+          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5451,10 +5505,14 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AK23" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5477,27 +5535,27 @@
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>化学制药</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5530,7 +5588,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26新和成股MTN002(科创债)</t>
+          <t>26华能新能SCP010</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5540,62 +5598,64 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683464.IB</t>
+          <t>012682177.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>1.35 ~ 1.55</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I24" s="3"/>
+        <v>1.38</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>16.28</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26新和成股SCP001(科创债)</t>
+          <t>26华能新能SCP009</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>60D</t>
+          <t>50D</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.5159</t>
+          <t>1.4780</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司</t>
+          <t>华能新能源股份有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 40.78</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5619,47 +5679,51 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.59</v>
+        <v>4.8</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.17</v>
+        <v>1.0</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
-        </is>
-      </c>
-      <c r="Y24" s="3"/>
+          <t>1.45%~1.49%</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
+          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5669,7 +5733,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
+          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5679,14 +5743,10 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5709,27 +5769,27 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>化学制药</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5762,7 +5822,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP010</t>
+          <t>26苏交通CP005</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5772,12 +5832,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>012682177.IB</t>
+          <t>042680304.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>0.99Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
@@ -5788,46 +5848,48 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.37 ~ 1.67</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="I25" s="3"/>
+        <v>1.42</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>19.68</v>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP009</t>
+          <t>26苏交通CP004</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>50D</t>
+          <t>354D</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.4780</t>
+          <t>1.5317</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.4900/--</t>
+          <t>1.5400/1.4293</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司</t>
+          <t>江苏交通控股有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>B- 38.13</t>
+          <t>B- 48.67</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5851,19 +5913,19 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.8</v>
+        <v>2.985</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.0</v>
+        <v>1.25</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5874,28 +5936,28 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
+          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5905,7 +5967,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
+          <t>江苏交通控股有限公司2026年度第五期短期融资券</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5915,7 +5977,7 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-08-27</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
@@ -5936,32 +5998,32 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5994,7 +6056,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26苏交通CP005</t>
+          <t>26无锡城南PPN001(取消发行)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6002,64 +6064,48 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>042680304.IB</t>
-        </is>
-      </c>
+      <c r="C26" s="3"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0.99Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>20.0</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.37 ~ 1.67</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>1.42</v>
-      </c>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>26苏交通CP004</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>354D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.4293</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司</t>
+          <t>无锡市城南建设投资发展有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>B- 45.00</t>
+          <t>C- 23.04</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6082,47 +6128,39 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U26" s="4" t="n">
-        <v>2.985</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>1.25</v>
-      </c>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t>1.50%~1.54%</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X26" s="3"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
+          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,杭州银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6137,17 +6175,17 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司2026年度第五期短期融资券</t>
+          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2027-08-27</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6168,12 +6206,12 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
@@ -6183,17 +6221,17 @@
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6226,86 +6264,110 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26无锡城南PPN001(取消发行)</t>
+          <t>26金霞01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
-        </is>
-      </c>
-      <c r="C27" s="3"/>
+          <t>08-31 19:00</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>283880.SH</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>37.94</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>25金霞01</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>4.13Y</t>
+        </is>
+      </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
+          <t>1.9567</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>湖南金霞发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>C- 10.76</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>08-31 15:00</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>无锡市城南建设投资发展有限公司</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t>C- 24.04</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>08-31 09:00</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U27" s="3"/>
+      <c r="U27" s="4" t="n">
+        <v>5.85</v>
+      </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X27" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>1.80%~1.90%</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6314,23 +6376,23 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6340,12 +6402,12 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
+          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6361,7 +6423,7 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6381,7 +6443,7 @@
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
@@ -6391,12 +6453,12 @@
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
@@ -6406,7 +6468,7 @@
       </c>
       <c r="AU27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AV27" s="3" t="inlineStr">
@@ -6416,7 +6478,7 @@
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
@@ -6434,17 +6496,17 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26光大01</t>
+          <t>26江津华信MTN001</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>524991.SZ</t>
+          <t>102683462.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -6453,51 +6515,55 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="I28" s="3"/>
+        <v>1.78</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>52.24</v>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24光大集团MTN004A</t>
+          <t>25江津华信MTN002A</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>3.93Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6671</t>
+          <t>1.8922</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 38.65</t>
+          <t>C- 20.66</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6507,7 +6573,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6517,65 +6583,65 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>5.6333</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>重庆市-江津区</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6585,64 +6651,64 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AK28" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO28" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ28" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR28" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6663,22 +6729,24 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ28" s="3"/>
+      <c r="AZ28" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26郴新01</t>
+          <t>26广州净水GN002</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:30</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>283833.SH</t>
+          <t>132600024.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -6687,36 +6755,40 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F29" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="I29" s="3"/>
+        <v>1.71</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>29.94</v>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>24郴新02</t>
+          <t>26广州净水GN001B</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>3.14Y</t>
+          <t>4.50Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2.2500</t>
+          <t>1.7922</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6726,12 +6798,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司</t>
+          <t>广州市净水有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.49</t>
+          <t>D+ 8.03</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6741,7 +6813,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6751,46 +6823,52 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U29" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>5.44</v>
+      </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>2.40%~2.50%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z29" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>湖南省-郴州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
+          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司</t>
+          <t>广发证券股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6800,28 +6878,28 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -6831,37 +6909,37 @@
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6894,96 +6972,98 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26金霞01</t>
+          <t>26温州交运MTN003(资产担保)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>283880.SH</t>
+          <t>102683428.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 1.79</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
         <v>1.79</v>
       </c>
-      <c r="I30" s="3"/>
+      <c r="I30" s="4" t="n">
+        <v>53.24</v>
+      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>26温州交运MTN002</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>2.86Y</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>1.7832</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>温州市交通运输集团有限公司</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>C- 18.95</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>08-31 09:00</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>25金霞01</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>4.13Y</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>1.9567</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>湖南金霞发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t>C- 10.34</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>08-31 15:00</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>5.85</v>
+        <v>0.4</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
@@ -6991,36 +7071,36 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t>1.80%~1.90%</t>
-        </is>
-      </c>
+      <c r="X30" s="3"/>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
+          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币，用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD30" s="3"/>
+          <t>浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr">
+        <is>
+          <t>温州交运集团房地产投资开发有限公司</t>
+        </is>
+      </c>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -7030,83 +7110,87 @@
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK30" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK30" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>公交</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO30" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ30" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR30" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
       <c r="AV30" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
@@ -7156,7 +7240,9 @@
       <c r="H31" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="I31" s="3"/>
+      <c r="I31" s="4" t="n">
+        <v>34.76</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t>1.65</t>
@@ -7189,7 +7275,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 18.99</t>
+          <t>C- 20.26</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7356,22 +7442,22 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26江津华信MTN001</t>
+          <t>26振兴Y2</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>102683462.IB</t>
+          <t>520449.SZ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -7382,31 +7468,33 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I32" s="3"/>
+        <v>2.28</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>86.94</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25江津华信MTN002A</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>3.93Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.8922</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7416,12 +7504,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 20.23</t>
+          <t>C- 15.54</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7431,7 +7519,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7441,23 +7529,21 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>5.6333</v>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>3.82</v>
+      </c>
+      <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>2.02%~2.12%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7468,23 +7554,27 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>重庆市-江津区</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD32" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr">
+        <is>
+          <t>天府信用增进股份有限公司</t>
+        </is>
+      </c>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7494,72 +7584,64 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK32" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP32" s="3"/>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7569,12 +7651,12 @@
       </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7587,29 +7669,27 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ32" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ32" s="3"/>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN002</t>
+          <t>26振兴Y3</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>132600024.IB</t>
+          <t>520450.SZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -7620,31 +7700,33 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.90 ~ 3.00</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="I33" s="3"/>
+        <v>2.35</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>93.94</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN001B</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.50Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7922</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7654,12 +7736,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.27</t>
+          <t>C- 15.54</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7669,7 +7751,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7679,52 +7761,52 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>5.44</v>
+        <v>2.88</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>2.17%~2.27%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中国银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>成都中小企业融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7734,68 +7816,64 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+      <c r="AP33" s="3"/>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7805,12 +7883,12 @@
       </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7828,17 +7906,17 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN003(资产担保)</t>
+          <t>26光大01</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>102683428.IB</t>
+          <t>524991.SZ</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7847,53 +7925,55 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.0</v>
+        <v>20.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.0</v>
+        <v>40.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.79</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="I34" s="3"/>
+        <v>1.55</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>29.24</v>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN002</t>
+          <t>24光大集团MTN004A</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.86Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.7832</t>
+          <t>1.6671</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司</t>
+          <t>中国光大集团股份公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 18.84</t>
+          <t>B- 37.31</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7903,7 +7983,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7913,61 +7993,67 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U34" s="3"/>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>3.47</v>
+      </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X34" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z34" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币，用于偿还金融机构借款</t>
+          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3" t="inlineStr">
-        <is>
-          <t>温州交运集团房地产投资开发有限公司</t>
-        </is>
-      </c>
+          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
+          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7977,57 +8063,57 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>2029-09-02</t>
         </is>
       </c>
       <c r="AK34" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8037,7 +8123,7 @@
       </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-31.xlsx
+++ b/data/credit_bond_all_2026-08-31.xlsx
@@ -2306,7 +2306,7 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN002</t>
+          <t>26太湖新城MTN010</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2316,64 +2316,64 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683460.IB</t>
+          <t>102683461.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.54</v>
+        <v>1.98</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>28.24</v>
+        <v>56.94</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN001</t>
+          <t>26太新Y3</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2.78Y</t>
+          <t>4.93Y+N</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.6734</t>
+          <t>1.8931</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司</t>
+          <t>无锡市太湖新城发展集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C 26.94</t>
+          <t>B- 36.75</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.66</v>
+        <v>2.89</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2420,17 +2420,17 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
+          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司</t>
+          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
+          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2461,14 +2461,10 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK10" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2486,12 +2482,12 @@
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
@@ -2501,17 +2497,17 @@
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2526,7 +2522,7 @@
       </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
@@ -2544,7 +2540,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26太湖新城MTN010</t>
+          <t>26高淳国资MTN001</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2554,64 +2550,64 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>102683461.IB</t>
+          <t>102690020.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>56.94</v>
+        <v>59.24</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26太新Y3</t>
+          <t>25高淳国资MTN002</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>4.93Y+N</t>
+          <t>3.63Y+N</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.8931</t>
+          <t>1.9715</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8700</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
+          <t>南京高淳国有资产经营控股集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 36.75</t>
+          <t>C- 14.34</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2635,40 +2631,40 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.89</v>
+        <v>5.05</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.92</v>
+        <v>5.38</v>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
+          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
+          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
@@ -2689,7 +2685,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
+          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2699,10 +2695,14 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK11" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK11" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL11" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AM11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN11" s="3" t="inlineStr">
@@ -2725,27 +2725,27 @@
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2778,7 +2778,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26高淳国资MTN001</t>
+          <t>26高教投资PPN002</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2788,64 +2788,64 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102690020.IB</t>
+          <t>032690012.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.0</v>
+        <v>4.17</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.0</v>
+        <v>4.17</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>59.24</v>
+        <v>54.76</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>25高淳国资MTN002</t>
+          <t>26高教投资PPN001</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>3.63Y+N</t>
+          <t>56D</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.9715</t>
+          <t>1.6401</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/1.8700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司</t>
+          <t>泰州高教投资发展有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 14.34</t>
+          <t>B- 40.98</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2869,14 +2869,14 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>5.05</v>
+        <v>2.4317</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>5.38</v>
+        <v>1.2</v>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
@@ -2886,29 +2886,29 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
+          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
+          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2923,24 +2923,20 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
+          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK12" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-09-01</t>
+        </is>
+      </c>
+      <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2948,7 +2944,7 @@
       </c>
       <c r="AM12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN12" s="3" t="inlineStr">
@@ -2958,32 +2954,32 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2998,7 +2994,7 @@
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -3011,64 +3007,66 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN002</t>
+          <t>26开滦Y1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>032690012.IB</t>
+          <t>245986.SH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.17</v>
+        <v>10.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.17</v>
+        <v>10.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>54.76</v>
+        <v>73.24</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN001</t>
+          <t>25开滦MTN001(科创票据)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>56D</t>
+          <t>1.38Y+2.00Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.6401</t>
+          <t>1.8119</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3078,12 +3076,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司</t>
+          <t>开滦(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 40.98</t>
+          <t>C- 24.06</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3093,7 +3091,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3103,50 +3101,48 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2.4317</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>4.03</v>
+      </c>
+      <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3156,68 +3152,72 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
+          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
-        </is>
-      </c>
-      <c r="AK13" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL13" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3245,29 +3245,27 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ13" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ13" s="3"/>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26开滦Y1</t>
+          <t>26知识城SCP002</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>245986.SH</t>
+          <t>012682176.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.27Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -3278,48 +3276,48 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.30 ~ 1.52</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>73.24</v>
+        <v>16.88</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25开滦MTN001(科创票据)</t>
+          <t>26知识城SCP001</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>1.38Y+2.00Y</t>
+          <t>122D</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.8119</t>
+          <t>1.5318</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.5000</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司</t>
+          <t>知识城(广州)投资集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 24.06</t>
+          <t>B- 42.68</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3329,7 +3327,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3339,21 +3337,23 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="V14" s="3"/>
+        <v>1.79</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3364,23 +3364,23 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
+          <t>本期超短期融资券基础发行规模0亿元,发行金额上限10亿元(含),用于偿还债务融资工具[25知识城SCP007]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
+          <t>浙商银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>知识城(广州)投资集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3405,157 +3405,155 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="AK14" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY14" s="3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO14" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ14" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR14" s="3" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>煤炭开采</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV14" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW14" s="3" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AX14" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26知识城SCP002</t>
+          <t>26振兴Y1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>012682176.IB</t>
+          <t>520448.SZ</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>0.27Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>10.0</v>
+        <v>2.5</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10.0</v>
+        <v>2.5</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.52</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.42</v>
+        <v>2.28</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>16.88</v>
+        <v>86.94</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26知识城SCP001</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>122D</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.5318</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>知识城(广州)投资集团有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>B- 42.68</t>
+          <t>C- 15.54</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3565,7 +3563,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3575,50 +3573,52 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V15" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.14</v>
+      </c>
+      <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行规模0亿元,发行金额上限10亿元(含),用于偿还债务融资工具[25知识城SCP007]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,渤海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD15" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr">
+        <is>
+          <t>重庆三峡融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3628,68 +3628,64 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>知识城(广州)投资集团有限公司2026年度第二期超短期融资券</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP15" s="3"/>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3699,12 +3695,12 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
@@ -3717,66 +3713,64 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y1</t>
+          <t>26江宁滨江PPN002</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>520448.SZ</t>
+          <t>032680505.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.28</v>
+        <v>1.73</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>86.94</v>
+        <v>47.76</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>25江宁滨江PPN004</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>2.18Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.8442</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3786,12 +3780,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>南京江宁滨江新城开发建设有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 15.54</t>
+          <t>C 25.68</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3801,7 +3795,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3811,52 +3805,50 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="V16" s="3"/>
+        <v>4.5217</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>重庆三峡融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3866,12 +3858,12 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
+          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3881,64 +3873,68 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>8*无效</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO16" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP16" s="3"/>
-      <c r="AQ16" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR16" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS16" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3951,12 +3947,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26江宁滨江PPN002</t>
+          <t>26盐城创投PPN001(混合型科创债)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3966,49 +3964,49 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>032680505.IB</t>
+          <t>032680495.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.3</v>
+        <v>2.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.3</v>
+        <v>2.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>2.15 ~ 3.05</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>47.76</v>
+        <v>96.94</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25江宁滨江PPN004</t>
+          <t>25盐创K1</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.18Y</t>
+          <t>4.16Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.8442</t>
+          <t>1.9798</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -4018,12 +4016,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司</t>
+          <t>盐城市创新创业投资有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C 25.68</t>
+          <t>C- 14.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4047,40 +4045,38 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.5217</v>
-      </c>
-      <c r="V17" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>1.85</v>
+      </c>
+      <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>2.35%~2.45%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
+          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
+          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4101,7 +4097,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
+          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4111,7 +4107,7 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
@@ -4122,7 +4118,7 @@
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4132,32 +4128,28 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>8*无效</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP17" s="3"/>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4192,17 +4184,17 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26盐城创投PPN001(混合型科创债)</t>
+          <t>26郴新01</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>032680495.IB</t>
+          <t>283833.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -4211,40 +4203,40 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.0</v>
+        <v>2.78</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.0</v>
+        <v>2.78</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2.15 ~ 3.05</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>96.94</v>
+        <v>91.94</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25盐创K1</t>
+          <t>24郴新02</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4.16Y</t>
+          <t>3.14Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.9798</t>
+          <t>2.2500</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -4254,12 +4246,12 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司</t>
+          <t>郴州市新天投资有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 14.00</t>
+          <t>C+ 31.72</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4269,7 +4261,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4279,48 +4271,48 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.85</v>
+        <v>3.79</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>2.35%~2.45%</t>
+          <t>2.40%~2.50%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>湖南省-郴州市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
+          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
+          <t>财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4330,12 +4322,12 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
+          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4345,49 +4337,53 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP18" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4415,66 +4411,64 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ18" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ18" s="3"/>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26郴新01</t>
+          <t>26宁沪高MTN002</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:30</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>283833.SH</t>
+          <t>102683460.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.78</v>
+        <v>5.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.78</v>
+        <v>5.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.33</v>
+        <v>1.54</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>91.94</v>
+        <v>28.24</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>24郴新02</t>
+          <t>26宁沪高MTN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>3.14Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2.2500</t>
+          <t>1.6734</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4484,12 +4478,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司</t>
+          <t>江苏宁沪高速公路股份有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.72</t>
+          <t>C 26.94</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4499,7 +4493,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4509,48 +4503,50 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="V19" s="3"/>
+        <v>4.66</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>2.40%~2.50%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>湖南省-郴州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
+          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司</t>
+          <t>华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4560,28 +4556,32 @@
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK19" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK19" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
@@ -4611,17 +4611,17 @@
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4654,53 +4654,59 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26宁波能源SCP002(取消发行)</t>
+          <t>26金霞01</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>DY012682180.IB</t>
+          <t>283880.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F20" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>37.94</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>GC甬能Y1</t>
+          <t>25金霞01</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>3.51Y+N</t>
+          <t>4.13Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.8509</t>
+          <t>1.9567</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4710,12 +4716,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司</t>
+          <t>湖南金霞发展集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 18.20</t>
+          <t>C- 10.76</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4725,7 +4731,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4738,47 +4744,45 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U20" s="3"/>
+      <c r="U20" s="4" t="n">
+        <v>5.85</v>
+      </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.64%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD20" s="3" t="inlineStr">
-        <is>
-          <t>宁波开发投资集团有限公司</t>
-        </is>
-      </c>
+          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4788,28 +4792,28 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券(取消发行)</t>
+          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2027-03-30</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
@@ -4824,47 +4828,47 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
@@ -4877,14 +4881,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ20" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ20" s="3"/>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN003</t>
+          <t>26宁波能源SCP002(取消发行)</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4894,49 +4896,43 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102690021.IB</t>
+          <t>DY012682180.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>84.24</v>
-      </c>
+          <t>1.40 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN002</t>
+          <t>GC甬能Y1</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.61Y</t>
+          <t>3.51Y+N</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>2.1005</t>
+          <t>1.8509</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4946,12 +4942,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司</t>
+          <t>宁波能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.77</t>
+          <t>C- 18.20</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4961,7 +4957,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>08-31 14:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4974,47 +4970,47 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U21" s="4" t="n">
-        <v>2.7667</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>2.31%~2.41%</t>
+          <t>1.60%~1.64%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
+          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD21" s="3"/>
+          <t>宁波银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>宁波开发投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5029,7 +5025,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
+          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券(取消发行)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5039,14 +5035,10 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK21" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-03-30</t>
+        </is>
+      </c>
+      <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5064,7 +5056,7 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
@@ -5074,22 +5066,22 @@
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5099,7 +5091,7 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW21" s="3" t="inlineStr">
@@ -5117,12 +5109,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP006</t>
+          <t>26青城租赁MTN003</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5132,64 +5126,64 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>012682178.IB</t>
+          <t>102690021.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.49</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>31.81</v>
+        <v>84.24</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP001(科创债)</t>
+          <t>26青城租赁MTN002</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>53D</t>
+          <t>2.61Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.5142</t>
+          <t>2.1005</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>青岛城乡建设融资租赁有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 38.22</t>
+          <t>C+ 32.77</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5199,7 +5193,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 14:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5213,17 +5207,19 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="V22" s="3"/>
+        <v>2.7667</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>2.31%~2.41%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5234,28 +5230,28 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
+          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -5265,7 +5261,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
+          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5275,10 +5271,14 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5296,32 +5296,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5354,7 +5354,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26新和成股MTN002(科创债)</t>
+          <t>26立讯精工SCP006</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102683464.IB</t>
+          <t>012682178.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -5380,48 +5380,48 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>1.20 ~ 1.49</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>34.24</v>
+        <v>31.81</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26新和成股SCP001(科创债)</t>
+          <t>26立讯精工SCP001(科创债)</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>60D</t>
+          <t>53D</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.5159</t>
+          <t>1.5142</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5000</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 21.00</t>
+          <t>B- 38.22</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5445,42 +5445,44 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0.92</v>
+      </c>
+      <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
-        </is>
-      </c>
-      <c r="Y23" s="3"/>
+          <t>1.49%~1.53%</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
+          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5495,7 +5497,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
+          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5505,14 +5507,10 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK23" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5535,27 +5533,27 @@
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>化学制药</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5588,7 +5586,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP010</t>
+          <t>26新和成股MTN002(科创债)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5598,64 +5596,64 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>012682177.IB</t>
+          <t>102683464.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>16.28</v>
+        <v>34.24</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP009</t>
+          <t>26新和成股SCP001(科创债)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>50D</t>
+          <t>60D</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.4780</t>
+          <t>1.5159</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.4900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司</t>
+          <t>浙江新和成股份有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 40.78</t>
+          <t>C- 21.00</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5679,51 +5677,47 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.8</v>
+        <v>1.59</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.0</v>
+        <v>1.17</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
+      <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
+          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5733,7 +5727,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
+          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5743,10 +5737,14 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="AK24" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK24" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5769,27 +5767,27 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>化学制药</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5822,7 +5820,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26苏交通CP005</t>
+          <t>26华能新能SCP010</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5832,12 +5830,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>042680304.IB</t>
+          <t>012682177.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>0.99Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
@@ -5848,48 +5846,48 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.37 ~ 1.67</t>
+          <t>1.35 ~ 1.55</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>19.68</v>
+        <v>16.28</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26苏交通CP004</t>
+          <t>26华能新能SCP009</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>354D</t>
+          <t>50D</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>1.4780</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.4293</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司</t>
+          <t>华能新能源股份有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>B- 48.67</t>
+          <t>B- 40.78</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5913,19 +5911,19 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.985</v>
+        <v>4.8</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.25</v>
+        <v>1.0</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5936,28 +5934,28 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
+          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,杭州银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5967,7 +5965,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司2026年度第五期短期融资券</t>
+          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5977,7 +5975,7 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2027-08-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
@@ -5998,32 +5996,32 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6056,7 +6054,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26无锡城南PPN001(取消发行)</t>
+          <t>26苏交通CP005</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6064,103 +6062,129 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>042680304.IB</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.99Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+          <t>1.37 ~ 1.67</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>19.68</v>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>26苏交通CP004</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>354D</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>1.5317</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>1.5400/1.4293</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>江苏交通控股有限公司</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>B- 48.67</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>08-31 09:00</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>无锡市城南建设投资发展有限公司</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t>C- 23.04</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>08-31 09:00</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+      <c r="U26" s="4" t="n">
+        <v>2.985</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X26" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
+          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6175,17 +6199,17 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
+          <t>江苏交通控股有限公司2026年度第五期短期融资券</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2027-08-27</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6206,12 +6230,12 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
@@ -6221,17 +6245,17 @@
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6264,59 +6288,41 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26金霞01</t>
+          <t>26无锡城南PPN001(取消发行)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>283880.SH</t>
-        </is>
-      </c>
+          <t>08-31 18:00</t>
+        </is>
+      </c>
+      <c r="C27" s="3"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>6.0</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>37.94</v>
-      </c>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>25金霞01</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>4.13Y</t>
-        </is>
-      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.9567</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -6326,12 +6332,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>湖南金霞发展集团有限公司</t>
+          <t>无锡市城南建设投资发展有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 10.76</t>
+          <t>C- 23.04</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6341,7 +6347,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6354,20 +6360,14 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U27" s="4" t="n">
-        <v>5.85</v>
-      </c>
+      <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t>1.80%~1.90%</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X27" s="3"/>
       <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6376,23 +6376,23 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
+          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6402,12 +6402,12 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6423,7 +6423,7 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AU27" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AV27" s="3" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-31.xlsx
+++ b/data/credit_bond_all_2026-08-31.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-03" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-04" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
     </row>
@@ -920,68 +920,74 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN003(科创债)(取消发行)</t>
+          <t>26越秀集团MTN004(绿色)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>08-31 11:30</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>DY102683466.IB</t>
+          <t>102683458.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+          <t>1.94 ~ 2.35</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>66.17</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN002(科创债)</t>
+          <t>26广越12</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>9.98Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.9088</t>
+          <t>2.3356</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.8950/1.8800</t>
+          <t>2.3500/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司</t>
+          <t>广州越秀集团股份有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>A 75.38</t>
+          <t>C+ 32.28</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -991,7 +997,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>08-31 11:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1001,19 +1007,21 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U4" s="3"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>1.15</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>2.24%~2.34%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1021,24 +1029,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行金额为5亿元,本期发行的募集资金扣除承销费后,拟全部用于置换发行人本期科技创新债券发行之日起一年以内用于科技创新领域股权投资或基金出资的自有资金投入。</t>
+          <t>发行人拟将本期绿色中期票据募集资金6亿元用于偿还发行人有息债务[21越秀集团GN002（革命老区）]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
+          <t>中国银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
@@ -1059,7 +1063,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司2026年度第三期科技创新债券(取消发行)</t>
+          <t>广州越秀集团股份有限公司2026年度第四期绿色中期票据</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1069,13 +1073,17 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK4" s="3"/>
+          <t>2036-08-31</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -1085,33 +1093,37 @@
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP4" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
@@ -1136,7 +1148,7 @@
       </c>
       <c r="AY4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ4" s="3"/>
@@ -1144,74 +1156,74 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN004(绿色)</t>
+          <t>26ZTTZK1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>08-31 11:30</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>102683458.IB</t>
+          <t>246000.SH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.94 ~ 2.35</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>66.17</v>
+        <v>39.94</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26广越12</t>
+          <t>25ZTTZK1</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>9.98Y</t>
+          <t>3.97Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>2.3356</t>
+          <t>1.7685</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>2.3500/--</t>
+          <t>--/1.8300</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司</t>
+          <t>中铁投资集团有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.93</t>
+          <t>D 4.00</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1221,7 +1233,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1231,21 +1243,21 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U5" s="4" t="n">
-        <v>1.15</v>
+        <v>3.75</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>2.24%~2.34%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1253,41 +1265,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z5" s="3"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期绿色中期票据募集资金6亿元用于偿还发行人有息债务[21越秀集团GN002（革命老区）]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将10亿元用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第四期绿色中期票据</t>
+          <t>中铁投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1297,17 +1313,13 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2036-08-31</t>
-        </is>
-      </c>
-      <c r="AK5" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
@@ -1317,7 +1329,7 @@
       </c>
       <c r="AN5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AO5" s="3" t="inlineStr">
@@ -1327,22 +1339,22 @@
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
@@ -1380,17 +1392,17 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26晋能电力GN005(碳中和债)</t>
+          <t>26光大02(取消发行)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>132680093.IB</t>
+          <t>DY524992.SZ</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1399,55 +1411,49 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>20.0</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>44.96</v>
-      </c>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>25晋能电力MTN002</t>
+          <t>21光大集团MTN001B</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>5.38Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.9709</t>
+          <t>1.7413</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司</t>
+          <t>中国光大集团股份公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.22</t>
+          <t>B- 37.75</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1457,7 +1463,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
@@ -1474,12 +1480,12 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1487,41 +1493,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z6" s="3"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>山西省-太原市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
+          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
+          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG6" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
+          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
@@ -1537,7 +1547,7 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr">
@@ -1552,32 +1562,32 @@
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1602,7 +1612,7 @@
       </c>
       <c r="AY6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ6" s="3"/>
@@ -1610,22 +1620,22 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26ZTTZK1</t>
+          <t>26沪盛K1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>246000.SH</t>
+          <t>245999.SH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -1640,44 +1650,44 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>39.94</v>
+        <v>29.17</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>25ZTTZK1</t>
+          <t>26国盛MTN003(科创债)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>3.97Y</t>
+          <t>9.88Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.7685</t>
+          <t>2.0875</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/1.8300</t>
+          <t>--/2.0700</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>中铁投资集团有限公司</t>
+          <t>上海国盛(集团)有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>D 4.00</t>
+          <t>C 26.09</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1701,17 +1711,17 @@
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>3.75</v>
+        <v>3.93</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1719,24 +1729,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将10亿元用于偿还有息负债</t>
+          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
@@ -1747,7 +1753,7 @@
       </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG7" s="3" t="inlineStr">
@@ -1757,7 +1763,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>中铁投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1767,13 +1773,13 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2036-09-02</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AM7" s="3" t="inlineStr">
@@ -1793,27 +1799,27 @@
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1846,100 +1852,110 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26光大02(取消发行)</t>
+          <t>26太湖新城MTN010</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>DY524992.SZ</t>
+          <t>102683461.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>56.94</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>26太新Y3</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>4.93Y+N</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>1.8931</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>无锡市太湖新城发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>B- 35.69</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>08-31 09:00</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>21光大集团MTN001B</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>4.95Y</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>1.7413</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>1.7600/--</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>中国光大集团股份公司</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>B- 37.31</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>08-31 15:00</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>1.92</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1947,45 +1963,41 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)(取消发行)</t>
+          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1995,60 +2007,60 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ8" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2056,7 +2068,7 @@
       </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -2074,74 +2086,74 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26沪盛K1</t>
+          <t>26高教投资PPN002</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:30</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>245999.SH</t>
+          <t>032690012.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.0</v>
+        <v>4.17</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10.0</v>
+        <v>4.17</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>29.17</v>
+        <v>54.76</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26国盛MTN003(科创债)</t>
+          <t>26高教投资PPN001</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>9.88Y</t>
+          <t>56D</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>2.0875</t>
+          <t>1.6401</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/2.0700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司</t>
+          <t>泰州高教投资发展有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 24.21</t>
+          <t>B- 42.33</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2151,7 +2163,7 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -2161,48 +2173,50 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="V9" s="3"/>
+        <v>2.4317</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
+          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2212,75 +2226,75 @@
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2036-09-02</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="AQ9" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR9" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2301,27 +2315,29 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26太湖新城MTN010</t>
+          <t>26开滦Y1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683461.IB</t>
+          <t>245986.SH</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -2332,33 +2348,33 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>56.94</v>
+        <v>73.24</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26太新Y3</t>
+          <t>25开滦MTN001(科创票据)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>4.93Y+N</t>
+          <t>1.38Y+2.00Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.8931</t>
+          <t>1.8119</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2368,12 +2384,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
+          <t>开滦(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 36.75</t>
+          <t>C- 24.06</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2383,7 +2399,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2393,23 +2409,21 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>1.92</v>
-      </c>
+        <v>4.03</v>
+      </c>
+      <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2420,23 +2434,23 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2446,12 +2460,12 @@
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
+          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2461,28 +2475,32 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK10" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK10" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL10" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
@@ -2492,22 +2510,22 @@
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2540,7 +2558,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26高淳国资MTN001</t>
+          <t>26知识城SCP002</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2550,64 +2568,64 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>102690020.IB</t>
+          <t>012682176.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.27Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.30 ~ 1.52</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>59.24</v>
+        <v>16.88</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>25高淳国资MTN002</t>
+          <t>26知识城SCP001</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>3.63Y+N</t>
+          <t>122D</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.9715</t>
+          <t>1.5318</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/1.8700</t>
+          <t>1.5300/1.5000</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司</t>
+          <t>知识城(广州)投资集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 14.34</t>
+          <t>B- 43.02</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2631,46 +2649,46 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>5.05</v>
+        <v>1.79</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>5.38</v>
+        <v>1.0</v>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
+          <t>本期超短期融资券基础发行规模0亿元,发行金额上限10亿元(含),用于偿还债务融资工具[25知识城SCP007]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
+          <t>浙商银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2685,7 +2703,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
+          <t>知识城(广州)投资集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2695,14 +2713,10 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK11" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2710,7 +2724,7 @@
       </c>
       <c r="AM11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN11" s="3" t="inlineStr">
@@ -2720,34 +2734,34 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR11" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS11" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>房屋建设</t>
-        </is>
-      </c>
       <c r="AU11" s="3" t="inlineStr">
         <is>
           <t/>
@@ -2760,7 +2774,7 @@
       </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -2773,64 +2787,66 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ11" s="3"/>
+      <c r="AZ11" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN002</t>
+          <t>26振兴Y1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>032690012.IB</t>
+          <t>520448.SZ</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.17</v>
+        <v>2.5</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.17</v>
+        <v>2.5</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>54.76</v>
+        <v>86.94</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN001</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>56D</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.6401</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2840,12 +2856,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 40.98</t>
+          <t>C- 13.46</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2855,7 +2871,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2865,50 +2881,52 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.4317</v>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>3.14</v>
+      </c>
+      <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>重庆三峡融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2918,12 +2936,12 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2933,53 +2951,49 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP12" s="3"/>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2989,12 +3003,12 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -3007,66 +3021,64 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26开滦Y1</t>
+          <t>26江宁滨江PPN002</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>245986.SH</t>
+          <t>032680505.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.0</v>
+        <v>2.3</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10.0</v>
+        <v>2.3</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>73.24</v>
+        <v>47.76</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>25开滦MTN001(科创票据)</t>
+          <t>25江宁滨江PPN004</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>1.38Y+2.00Y</t>
+          <t>2.18Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.8119</t>
+          <t>1.8442</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3076,12 +3088,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司</t>
+          <t>南京江宁滨江新城开发建设有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 24.06</t>
+          <t>C 29.39</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3091,7 +3103,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3101,13 +3113,15 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="V13" s="3"/>
+        <v>4.5217</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
           <t>6-</t>
@@ -3115,34 +3129,34 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
+          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
+          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3152,105 +3166,103 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="AK13" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-09-01</t>
+        </is>
+      </c>
+      <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>8*无效</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM13" s="3" t="inlineStr">
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY13" s="3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO13" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ13" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR13" s="3" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>煤炭开采</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW13" s="3" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AX13" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AZ13" s="3"/>
+      <c r="AZ13" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26知识城SCP002</t>
+          <t>26盐城创投PPN001(混合型科创债)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3260,64 +3272,64 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>012682176.IB</t>
+          <t>032680495.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0.27Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.52</t>
+          <t>2.15 ~ 3.05</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>16.88</v>
+        <v>96.94</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26知识城SCP001</t>
+          <t>25盐创K1</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>122D</t>
+          <t>4.16Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.5318</t>
+          <t>1.9798</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>知识城(广州)投资集团有限公司</t>
+          <t>盐城市创新创业投资有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 42.68</t>
+          <t>C 26.50</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3341,46 +3353,44 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>1.85</v>
+      </c>
+      <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>2.35%~2.45%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行规模0亿元,发行金额上限10亿元(含),用于偿还债务融资工具[25知识城SCP007]</t>
+          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,渤海银行股份有限公司</t>
+          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3395,17 +3405,17 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>知识城(广州)投资集团有限公司2026年度第二期超短期融资券</t>
+          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
@@ -3416,7 +3426,7 @@
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
@@ -3426,27 +3436,23 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP14" s="3"/>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
@@ -3480,65 +3486,65 @@
         </is>
       </c>
       <c r="AZ14" s="4" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y1</t>
+          <t>26郴新01</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>520448.SZ</t>
+          <t>283833.SH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>86.94</v>
+        <v>91.94</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>24郴新02</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>3.14Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>2.2500</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3548,12 +3554,12 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>郴州市新天投资有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 15.54</t>
+          <t>C- 17.08</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3563,7 +3569,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3577,45 +3583,41 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.14</v>
+        <v>3.79</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>2.40%~2.50%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>湖南省-郴州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>重庆三峡融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>财信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3628,12 +3630,12 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
+          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3649,58 +3651,62 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO15" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP15" s="3"/>
-      <c r="AQ15" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR15" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
@@ -3718,7 +3724,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26江宁滨江PPN002</t>
+          <t>26宁沪高MTN002</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3728,64 +3734,64 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>032680505.IB</t>
+          <t>102683460.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.3</v>
+        <v>5.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.3</v>
+        <v>5.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>47.76</v>
+        <v>28.24</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>25江宁滨江PPN004</t>
+          <t>26宁沪高MTN001</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.18Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.8442</t>
+          <t>1.6734</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司</t>
+          <t>江苏宁沪高速公路股份有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C 25.68</t>
+          <t>C+ 34.01</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3809,24 +3815,24 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.5217</v>
+        <v>4.66</v>
       </c>
       <c r="V16" s="4" t="n">
         <v>1.5</v>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
@@ -3837,18 +3843,18 @@
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
+          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
+          <t>华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3863,20 +3869,24 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
+          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
-        </is>
-      </c>
-      <c r="AK16" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK16" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3894,12 +3904,12 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>8*无效</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
@@ -3909,17 +3919,17 @@
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3947,66 +3957,64 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ16" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ16" s="3"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26盐城创投PPN001(混合型科创债)</t>
+          <t>26金霞01</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>032680495.IB</t>
+          <t>283880.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2.15 ~ 3.05</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.38</v>
+        <v>1.79</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>96.94</v>
+        <v>37.94</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25盐创K1</t>
+          <t>25金霞01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.16Y</t>
+          <t>4.13Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.9798</t>
+          <t>1.9567</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -4016,12 +4024,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司</t>
+          <t>湖南金霞发展集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 14.00</t>
+          <t>C- 10.26</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4031,7 +4039,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -4045,17 +4053,17 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.85</v>
+        <v>5.85</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>2.35%~2.45%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4066,23 +4074,23 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
+          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4092,12 +4100,12 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
+          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4113,12 +4121,12 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4128,33 +4136,37 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP17" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
@@ -4164,7 +4176,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4177,81 +4189,79 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ17" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ17" s="3"/>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26郴新01</t>
+          <t>26高淳国资MTN001</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:30</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>283833.SH</t>
+          <t>102690020.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.78</v>
+        <v>4.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.78</v>
+        <v>4.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>91.94</v>
+        <v>59.24</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>24郴新02</t>
+          <t>25高淳国资MTN002</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.14Y</t>
+          <t>3.63Y+N</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2.2500</t>
+          <t>1.9715</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8700</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司</t>
+          <t>南京高淳国有资产经营控股集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.72</t>
+          <t>C- 16.69</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4261,7 +4271,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4271,48 +4281,50 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="V18" s="3"/>
+        <v>5.05</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>5.38</v>
+      </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>2.40%~2.50%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>湖南省-郴州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
+          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司</t>
+          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4322,75 +4334,79 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK18" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL18" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ18" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR18" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4398,7 +4414,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4416,7 +4432,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN002</t>
+          <t>26宁波能源SCP002(取消发行)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4426,49 +4442,43 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683460.IB</t>
+          <t>DY012682180.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F19" s="4" t="n">
-        <v>5.0</v>
-      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>28.24</v>
-      </c>
+          <t>1.40 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN001</t>
+          <t>GC甬能Y1</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.78Y</t>
+          <t>3.51Y+N</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.6734</t>
+          <t>1.8509</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4478,12 +4488,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司</t>
+          <t>宁波能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C 26.94</t>
+          <t>C- 18.20</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4506,47 +4516,47 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U19" s="4" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.60%~1.64%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
+          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD19" s="3"/>
+          <t>宁波银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr">
+        <is>
+          <t>宁波开发投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4561,7 +4571,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
+          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券(取消发行)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4571,14 +4581,10 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK19" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-03-30</t>
+        </is>
+      </c>
+      <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -4601,27 +4607,27 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4631,7 +4637,7 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW19" s="3" t="inlineStr">
@@ -4649,140 +4655,138 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ19" s="3"/>
+      <c r="AZ19" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26金霞01</t>
+          <t>26厦门产投MTN003(科创债)(取消发行)</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>283880.SH</t>
+          <t>DY102683466.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>6.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>37.94</v>
-      </c>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>26厦门产投MTN002(科创债)</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>4.92Y</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>1.9088</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>1.8950/1.8800</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>厦门市产业投资有限公司</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>A 75.38</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>08-31 11:00</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>25金霞01</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>4.13Y</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>1.9567</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>湖南金霞发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t>C- 10.76</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>08-31 15:00</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="n">
-        <v>5.85</v>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z20" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
+          <t>本期科技创新债券发行金额为5亿元,本期发行的募集资金扣除承销费后,拟全部用于置换发行人本期科技创新债券发行之日起一年以内用于科技创新领域股权投资或基金出资的自有资金投入。</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
+          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4792,28 +4796,28 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>厦门市产业投资有限公司2026年度第三期科技创新债券(取消发行)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
@@ -4823,62 +4827,58 @@
       </c>
       <c r="AN20" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP20" s="3"/>
+      <c r="AQ20" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY20" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO20" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ20" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR20" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW20" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AX20" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ20" s="3"/>
@@ -4886,7 +4886,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26宁波能源SCP002(取消发行)</t>
+          <t>26青城租赁MTN003</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4896,43 +4896,49 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>DY012682180.IB</t>
+          <t>102690021.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>84.24</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>GC甬能Y1</t>
+          <t>26青城租赁MTN002</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>3.51Y+N</t>
+          <t>2.61Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.8509</t>
+          <t>2.1005</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4942,12 +4948,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司</t>
+          <t>青岛城乡建设融资租赁有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 18.20</t>
+          <t>C+ 33.47</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4957,7 +4963,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 14:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4970,47 +4976,47 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
+      <c r="U21" s="4" t="n">
+        <v>2.7667</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.64%</t>
+          <t>2.31%~2.41%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
+          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD21" s="3" t="inlineStr">
-        <is>
-          <t>宁波开发投资集团有限公司</t>
-        </is>
-      </c>
+          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5025,7 +5031,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券(取消发行)</t>
+          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5035,10 +5041,14 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2027-03-30</t>
-        </is>
-      </c>
-      <c r="AK21" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK21" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5056,7 +5066,7 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
@@ -5066,22 +5076,22 @@
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5091,7 +5101,7 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW21" s="3" t="inlineStr">
@@ -5109,14 +5119,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ21" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ21" s="3"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN003</t>
+          <t>26立讯精工SCP006</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5126,64 +5134,64 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>102690021.IB</t>
+          <t>012682178.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.20 ~ 1.49</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>84.24</v>
+        <v>31.81</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26青城租赁MTN002</t>
+          <t>26立讯精工SCP001(科创债)</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.61Y</t>
+          <t>53D</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2.1005</t>
+          <t>1.5142</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5000</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.77</t>
+          <t>B- 37.88</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5193,7 +5201,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>08-31 14:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5207,19 +5215,17 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.7667</v>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>0.92</v>
+      </c>
+      <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>2.31%~2.41%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5230,28 +5236,28 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额不超过3亿元,将全部用于偿还发行人到期债务融资工具本金[25青城租赁SCP002]</t>
+          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,浙商银行股份有限公司</t>
+          <t>杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -5261,7 +5267,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>青岛城乡建设融资租赁有限公司2026年度第三期中期票据</t>
+          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5271,14 +5277,10 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK22" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5296,32 +5298,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5354,7 +5356,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP006</t>
+          <t>26新和成股MTN002(科创债)</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5364,12 +5366,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>012682178.IB</t>
+          <t>102683464.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -5380,48 +5382,48 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.49</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>31.81</v>
+        <v>34.24</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP001(科创债)</t>
+          <t>26新和成股SCP001(科创债)</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>53D</t>
+          <t>60D</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.5142</t>
+          <t>1.5159</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>浙江新和成股份有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B- 38.22</t>
+          <t>B- 37.67</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5445,44 +5447,42 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="V23" s="3"/>
+        <v>1.59</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.17</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
-        </is>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
+      <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
+          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司2026年度第六期超短期融资券</t>
+          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5507,10 +5507,14 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AK23" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5533,27 +5537,27 @@
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>化学制药</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5586,7 +5590,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26新和成股MTN002(科创债)</t>
+          <t>26华能新能SCP010</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5596,64 +5600,64 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683464.IB</t>
+          <t>012682177.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>1.35 ~ 1.55</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>34.24</v>
+        <v>16.28</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26新和成股SCP001(科创债)</t>
+          <t>26华能新能SCP009</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>60D</t>
+          <t>50D</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.5159</t>
+          <t>1.4780</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司</t>
+          <t>华能新能源股份有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C- 21.00</t>
+          <t>B- 41.47</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5677,47 +5681,51 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.59</v>
+        <v>4.8</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.17</v>
+        <v>1.0</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
-        </is>
-      </c>
-      <c r="Y24" s="3"/>
+          <t>1.45%~1.49%</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>首期发行金额10亿元,拟全部用于偿还有息负债</t>
+          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5727,7 +5735,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>浙江新和成股份有限公司2026年度第二期科技创新债券</t>
+          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5737,14 +5745,10 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -5767,27 +5771,27 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>化学制药</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5820,7 +5824,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP010</t>
+          <t>26苏交通CP005</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5830,12 +5834,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>012682177.IB</t>
+          <t>042680304.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>0.99Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
@@ -5846,48 +5850,48 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.37 ~ 1.67</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>16.28</v>
+        <v>19.68</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26华能新能SCP009</t>
+          <t>26苏交通CP004</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>50D</t>
+          <t>354D</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.4780</t>
+          <t>1.5317</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.4900/--</t>
+          <t>1.5400/1.4293</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司</t>
+          <t>江苏交通控股有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>B- 40.78</t>
+          <t>B- 48.00</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5911,19 +5915,19 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.8</v>
+        <v>2.985</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.0</v>
+        <v>1.25</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5934,28 +5938,28 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金20亿元,所募集资金拟全部用于偿还发行人及其子公司有息债务、补充营运资金</t>
+          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,平安银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5965,7 +5969,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>华能新能源股份有限公司2026年度第十期超短期融资券</t>
+          <t>江苏交通控股有限公司2026年度第五期短期融资券</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5975,7 +5979,7 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-08-27</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
@@ -5996,32 +6000,32 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6054,7 +6058,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26苏交通CP005</t>
+          <t>26无锡城南PPN001(取消发行)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6062,66 +6066,48 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>042680304.IB</t>
-        </is>
-      </c>
+      <c r="C26" s="3"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0.99Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>20.0</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.37 ~ 1.67</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>19.68</v>
-      </c>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>26苏交通CP004</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>354D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.4293</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司</t>
+          <t>无锡市城南建设投资发展有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>B- 48.67</t>
+          <t>C- 23.28</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6144,47 +6130,39 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U26" s="4" t="n">
-        <v>2.985</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>1.25</v>
-      </c>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t>1.50%~1.54%</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X26" s="3"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券募集资金20亿元,用于归还公司及子公司到期债务</t>
+          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,杭州银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6199,17 +6177,17 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>江苏交通控股有限公司2026年度第五期短期融资券</t>
+          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2027-08-27</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6230,12 +6208,12 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
@@ -6245,17 +6223,17 @@
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6288,7 +6266,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26无锡城南PPN001(取消发行)</t>
+          <t>26江津华信MTN001</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6296,78 +6274,104 @@
           <t>08-31 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>102683462.IB</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>52.24</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>25江津华信MTN002A</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>3.93Y</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>1.8922</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>重庆市江津区华信资产经营(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>C- 18.40</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>08-31 09:00</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>无锡市城南建设投资发展有限公司</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t>C- 23.04</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>08-31 09:00</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
+      <c r="U27" s="4" t="n">
+        <v>5.6333</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X27" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6376,23 +6380,23 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>重庆市-江津区</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具注册金额7亿元，本期发行3.6亿元，募集资金拟用于偿还发行人有息债务。[23无锡城南PPN001]</t>
+          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6407,20 +6411,24 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>无锡市城南建设投资发展有限公司2026年度第一期定向债务融资工具(取消发行)</t>
+          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -6438,12 +6446,12 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
@@ -6491,12 +6499,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ27" s="3"/>
+      <c r="AZ27" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26江津华信MTN001</t>
+          <t>26广州净水GN002</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6506,49 +6516,49 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>102683462.IB</t>
+          <t>132600024.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.0</v>
+        <v>2.5</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.0</v>
+        <v>2.5</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>52.24</v>
+        <v>29.94</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25江津华信MTN002A</t>
+          <t>26广州净水GN001B</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>3.93Y</t>
+          <t>4.50Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.8922</t>
+          <t>1.7922</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6558,12 +6568,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司</t>
+          <t>广州市净水有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 20.66</t>
+          <t>D+ 8.79</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6587,40 +6597,42 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>5.6333</v>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>5.44</v>
+      </c>
+      <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z28" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>重庆市-江津区</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行规模0亿元,发行金额上限3.00亿元,募集资金拟全部用于偿还发行人的债务融资工具本金[25江津华信CP003]</t>
+          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,重庆农村商业银行股份有限公司</t>
+          <t>广发证券股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6641,7 +6653,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>重庆市江津区华信资产经营(集团)有限公司2026年度第一期中期票据</t>
+          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6651,14 +6663,10 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK28" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -6676,32 +6684,32 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6729,14 +6737,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ28" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ28" s="3"/>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN002</t>
+          <t>26温州交运MTN003(资产担保)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6746,49 +6752,49 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>132600024.IB</t>
+          <t>102683428.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.5</v>
+        <v>1.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.5</v>
+        <v>1.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.50 ~ 1.79</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>29.94</v>
+        <v>53.24</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26广州净水GN001B</t>
+          <t>26温州交运MTN002</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.50Y</t>
+          <t>2.86Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7922</t>
+          <t>1.7832</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6798,12 +6804,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司</t>
+          <t>温州市交通运输集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.03</t>
+          <t>C- 19.31</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6827,45 +6833,41 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>5.44</v>
+        <v>0.4</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t>1.74%~1.84%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X29" s="3"/>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期绿色中期票据募集资金不超过2.5亿元(含),扣除承销费用后,拟使用4,600万元用于偿还沥滘项目等8个城镇污水处理项目的银行贷款本息,剩余资金用于补充沥滘项目等8个城镇污水处理绿色项目的药剂费、电费、水费、固定资产购置及更新改造、设施设备维护保养、污泥处理</t>
+          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币，用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中国银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD29" s="3"/>
+          <t>浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr">
+        <is>
+          <t>温州交运集团房地产投资开发有限公司</t>
+        </is>
+      </c>
       <c r="AE29" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -6883,7 +6885,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司2026年度第二期绿色中期票据</t>
+          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6893,10 +6895,14 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -6919,27 +6925,27 @@
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>非盈利性交运服务</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>非盈利性交运服务</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6949,7 +6955,7 @@
       </c>
       <c r="AV29" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW29" s="3" t="inlineStr">
@@ -6972,7 +6978,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN003(资产担保)</t>
+          <t>26淮安国投MTN005</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6982,64 +6988,64 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>102683428.IB</t>
+          <t>102683459.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.79</t>
+          <t>1.30 ~ 2.10</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>53.24</v>
+        <v>34.76</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN002</t>
+          <t>25淮安国投MTN003</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.86Y</t>
+          <t>1.66Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.7832</t>
+          <t>1.6367</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6000</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 18.95</t>
+          <t>C- 21.05</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7063,41 +7069,43 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V30" s="3"/>
+        <v>6.05</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X30" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币，用于偿还金融机构借款</t>
+          <t>本期发行金额2亿元,本次中期票据募集资金拟全部用于偿还发行人到期债券。[23 淮安国投MTN004]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD30" s="3" t="inlineStr">
-        <is>
-          <t>温州交运集团房地产投资开发有限公司</t>
-        </is>
-      </c>
+          <t>徽商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -7115,7 +7123,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7125,14 +7133,10 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-09-01</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -7150,32 +7154,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7185,7 +7189,7 @@
       </c>
       <c r="AV30" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW30" s="3" t="inlineStr">
@@ -7208,74 +7212,74 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26淮安国投MTN005</t>
+          <t>26振兴Y2</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>102683459.IB</t>
+          <t>520449.SZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.10</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>34.76</v>
+        <v>86.94</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>25淮安国投MTN003</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1.66Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.6367</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/1.6000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 20.26</t>
+          <t>C- 13.46</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7285,7 +7289,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7295,50 +7299,52 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>3.82</v>
+      </c>
+      <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>2.02%~2.12%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元,本次中期票据募集资金拟全部用于偿还发行人到期债券。[23 淮安国投MTN004]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD31" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr">
+        <is>
+          <t>天府信用增进股份有限公司</t>
+        </is>
+      </c>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7348,68 +7354,64 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年度第五期中期票据</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP31" s="3"/>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7419,12 +7421,12 @@
       </c>
       <c r="AV31" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7442,7 +7444,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y2</t>
+          <t>26振兴Y3</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7452,7 +7454,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>520449.SZ</t>
+          <t>520450.SZ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -7461,25 +7463,25 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.0</v>
+        <v>2.5</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.0</v>
+        <v>2.5</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.90 ~ 3.00</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>86.94</v>
+        <v>93.94</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -7509,7 +7511,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 15.54</t>
+          <t>C- 13.46</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7533,7 +7535,7 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.82</v>
+        <v>2.88</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
@@ -7543,7 +7545,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>2.02%~2.12%</t>
+          <t>2.17%~2.27%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7569,7 +7571,7 @@
       </c>
       <c r="AD32" s="3" t="inlineStr">
         <is>
-          <t>天府信用增进股份有限公司</t>
+          <t>成都中小企业融资担保有限责任公司</t>
         </is>
       </c>
       <c r="AE32" s="3" t="inlineStr">
@@ -7589,7 +7591,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7674,7 +7676,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y3</t>
+          <t>26光大01</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7684,64 +7686,64 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>520450.SZ</t>
+          <t>524991.SZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.5</v>
+        <v>20.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.5</v>
+        <v>40.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 3.00</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>93.94</v>
+        <v>29.24</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>24光大集团MTN004A</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.6671</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>中国光大集团股份公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 15.54</t>
+          <t>B- 37.75</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7765,45 +7767,45 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.88</v>
+        <v>3.47</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z33" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3" t="inlineStr">
-        <is>
-          <t>成都中小企业融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7811,7 +7813,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -7821,20 +7823,24 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
+          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7852,30 +7858,34 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP33" s="3"/>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
       <c r="AU33" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7883,12 +7893,12 @@
       </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7906,74 +7916,74 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26光大01</t>
+          <t>26晋能电力GN005(碳中和债)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>524991.SZ</t>
+          <t>132680093.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>40.0</v>
+        <v>5.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.70 ~ 2.10</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>29.24</v>
+        <v>44.96</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>24光大集团MTN004A</t>
+          <t>25晋能电力MTN002</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>5.38Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6671</t>
+          <t>1.9709</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司</t>
+          <t>晋能控股电力集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 37.31</t>
+          <t>C+ 34.39</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7983,7 +7993,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7997,17 +8007,17 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.47</v>
+        <v>3.24</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -8015,45 +8025,41 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山西省-太原市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
+          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8063,64 +8069,60 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO34" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR34" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8138,7 +8140,7 @@
       </c>
       <c r="AY34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AZ34" s="3"/>

--- a/data/credit_bond_all_2026-08-31.xlsx
+++ b/data/credit_bond_all_2026-08-31.xlsx
@@ -1620,22 +1620,22 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26沪盛K1</t>
+          <t>26太湖新城MTN010</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:30</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>245999.SH</t>
+          <t>102683461.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -1646,48 +1646,48 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
         <v>1.98</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>29.17</v>
+        <v>56.94</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26国盛MTN003(科创债)</t>
+          <t>26太新Y3</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>9.88Y</t>
+          <t>4.93Y+N</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2.0875</t>
+          <t>1.8931</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/2.0700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司</t>
+          <t>无锡市太湖新城发展集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C 26.09</t>
+          <t>B- 35.69</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1707,21 +1707,23 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="V7" s="3"/>
+        <v>2.89</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>1.92</v>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1732,23 +1734,23 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
+          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1758,12 +1760,12 @@
       </c>
       <c r="AG7" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1773,13 +1775,13 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2036-09-02</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM7" s="3" t="inlineStr">
@@ -1789,37 +1791,37 @@
       </c>
       <c r="AN7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1834,7 +1836,7 @@
       </c>
       <c r="AW7" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX7" s="3" t="inlineStr">
@@ -1852,7 +1854,7 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26太湖新城MTN010</t>
+          <t>26高教投资PPN002</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1862,49 +1864,49 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>102683461.IB</t>
+          <t>032690012.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.0</v>
+        <v>4.17</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.0</v>
+        <v>4.17</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>56.94</v>
+        <v>54.76</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26太新Y3</t>
+          <t>26高教投资PPN001</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>4.93Y+N</t>
+          <t>56D</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.8931</t>
+          <t>1.6401</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1914,12 +1916,12 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
+          <t>泰州高教投资发展有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>B- 35.69</t>
+          <t>B- 42.33</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1943,46 +1945,46 @@
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>2.89</v>
+        <v>2.4317</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.92</v>
+        <v>1.2</v>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额10亿元,募集资金将全部用于归还发行人本部债务融资工具本金[22太湖新城MTN002]</t>
+          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,南京银行股份有限公司</t>
+          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1997,17 +1999,17 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司2026年度第十期中期票据</t>
+          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
@@ -2028,12 +2030,12 @@
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
@@ -2043,12 +2045,12 @@
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
@@ -2068,7 +2070,7 @@
       </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -2081,64 +2083,66 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ8" s="3"/>
+      <c r="AZ8" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN002</t>
+          <t>26开滦Y1</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>032690012.IB</t>
+          <t>245986.SH</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.17</v>
+        <v>10.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.17</v>
+        <v>10.0</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>54.76</v>
+        <v>73.24</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26高教投资PPN001</t>
+          <t>25开滦MTN001(科创票据)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>56D</t>
+          <t>1.38Y+2.00Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.6401</t>
+          <t>1.8119</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2148,12 +2152,12 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司</t>
+          <t>开滦(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>B- 42.33</t>
+          <t>C- 24.06</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2163,7 +2167,7 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -2173,50 +2177,48 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.4317</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>4.03</v>
+      </c>
+      <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额4.17亿元,拟用于偿还发行人债务融资工具本金[26高教投资SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司,上海银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2226,68 +2228,72 @@
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>泰州高教投资发展有限公司2026年度第二期定向债务融资工具</t>
+          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
-        </is>
-      </c>
-      <c r="AK9" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK9" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2302,7 +2308,7 @@
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr">
@@ -2315,29 +2321,27 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ9" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ9" s="3"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26开滦Y1</t>
+          <t>26知识城SCP002</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>245986.SH</t>
+          <t>012682176.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.27Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -2348,48 +2352,48 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.30 ~ 1.52</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>73.24</v>
+        <v>16.88</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>25开滦MTN001(科创票据)</t>
+          <t>26知识城SCP001</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>1.38Y+2.00Y</t>
+          <t>122D</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.8119</t>
+          <t>1.5318</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.5000</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司</t>
+          <t>知识城(广州)投资集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 24.06</t>
+          <t>B- 43.02</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2399,7 +2403,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2409,21 +2413,23 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="V10" s="3"/>
+        <v>1.79</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2434,23 +2440,23 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期债务；本期债券募集资金100,000.00万元全部用于偿还公司有息债务。</t>
+          <t>本期超短期融资券基础发行规模0亿元,发行金额上限10亿元(含),用于偿还债务融资工具[25知识城SCP007]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,财达证券股份有限公司,国金证券股份有限公司</t>
+          <t>浙商银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2460,12 +2466,12 @@
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>开滦(集团)有限责任公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>知识城(广州)投资集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2475,157 +2481,155 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="AK10" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM10" s="3" t="inlineStr">
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY10" s="3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO10" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ10" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR10" s="3" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>煤炭开采</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW10" s="3" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AX10" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AZ10" s="3"/>
+      <c r="AZ10" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26知识城SCP002</t>
+          <t>26振兴Y1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>012682176.IB</t>
+          <t>520448.SZ</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0.27Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.0</v>
+        <v>2.5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.0</v>
+        <v>2.5</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.52</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.42</v>
+        <v>2.28</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>16.88</v>
+        <v>86.94</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26知识城SCP001</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>122D</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.5318</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>知识城(广州)投资集团有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 43.02</t>
+          <t>C- 13.46</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2635,7 +2639,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2645,50 +2649,52 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.14</v>
+      </c>
+      <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行规模0亿元,发行金额上限10亿元(含),用于偿还债务融资工具[25知识城SCP007]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,渤海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD11" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>重庆三峡融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2698,68 +2704,64 @@
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>知识城(广州)投资集团有限公司2026年度第二期超短期融资券</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP11" s="3"/>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2769,12 +2771,12 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -2787,66 +2789,64 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ11" s="4" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="AZ11" s="3"/>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y1</t>
+          <t>26江宁滨江PPN002</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>520448.SZ</t>
+          <t>032680505.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.28</v>
+        <v>1.73</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>86.94</v>
+        <v>47.76</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>25江宁滨江PPN004</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>2.18Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.8442</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>南京江宁滨江新城开发建设有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 13.46</t>
+          <t>C 29.39</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2881,52 +2881,50 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="V12" s="3"/>
+        <v>4.5217</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>重庆三峡融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2936,12 +2934,12 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
+          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2951,64 +2949,68 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>8*无效</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP12" s="3"/>
-      <c r="AQ12" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -3021,12 +3023,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26江宁滨江PPN002</t>
+          <t>26盐城创投PPN001(混合型科创债)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3036,49 +3040,49 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>032680505.IB</t>
+          <t>032680495.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.3</v>
+        <v>2.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.3</v>
+        <v>2.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>2.15 ~ 3.05</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>47.76</v>
+        <v>96.94</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>25江宁滨江PPN004</t>
+          <t>25盐创K1</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.18Y</t>
+          <t>4.16Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.8442</t>
+          <t>1.9798</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3088,12 +3092,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司</t>
+          <t>盐城市创新创业投资有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C 29.39</t>
+          <t>C 26.50</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3117,40 +3121,38 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>4.5217</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>1.85</v>
+      </c>
+      <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>2.35%~2.45%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本次发行2.30亿元,拟全部用于偿还发行人本部的债务融资工具本金[25江宁滨江PPN005]</t>
+          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,西部证券股份有限公司</t>
+          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
@@ -3171,7 +3173,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>南京江宁滨江新城开发建设有限公司2026年度第二期定向债务融资工具</t>
+          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3181,7 +3183,7 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
@@ -3192,7 +3194,7 @@
       </c>
       <c r="AM13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN13" s="3" t="inlineStr">
@@ -3202,32 +3204,28 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>8*无效</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP13" s="3"/>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3262,17 +3260,17 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26盐城创投PPN001(混合型科创债)</t>
+          <t>26郴新01</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>032680495.IB</t>
+          <t>283833.SH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3281,40 +3279,40 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.0</v>
+        <v>2.78</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.0</v>
+        <v>2.78</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2.15 ~ 3.05</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>96.94</v>
+        <v>91.94</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25盐创K1</t>
+          <t>24郴新02</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>4.16Y</t>
+          <t>3.14Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.9798</t>
+          <t>2.2500</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3324,12 +3322,12 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司</t>
+          <t>郴州市新天投资有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C 26.50</t>
+          <t>C- 17.08</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3339,7 +3337,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3349,48 +3347,48 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.85</v>
+        <v>3.79</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>2.35%~2.45%</t>
+          <t>2.40%~2.50%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>湖南省-郴州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本次注册额度为2亿元,全部用于置换前期一年以内投资于科技创新企业的基金出资</t>
+          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,南京银行股份有限公司</t>
+          <t>财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3400,12 +3398,12 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>盐城市创新创业投资有限公司2026年度第一期定向混合型科技创新债券</t>
+          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3415,49 +3413,53 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP14" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3485,81 +3487,79 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ14" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ14" s="3"/>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26郴新01</t>
+          <t>26宁沪高MTN002</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:30</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>283833.SH</t>
+          <t>102683460.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.78</v>
+        <v>5.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.78</v>
+        <v>5.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.33</v>
+        <v>1.54</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>91.94</v>
+        <v>28.24</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>24郴新02</t>
+          <t>26宁沪高MTN001</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>3.14Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>2.2500</t>
+          <t>1.6734</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司</t>
+          <t>江苏宁沪高速公路股份有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 17.08</t>
+          <t>C+ 34.01</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>08-31 16:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3579,48 +3579,50 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="V15" s="3"/>
+        <v>4.66</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>2.40%~2.50%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>湖南省-郴州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过2.78亿元(含2.78亿元)，扣除发行费用后，拟全部用于偿还到期公司债券“23郴新01”本金[23郴新01]</t>
+          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司</t>
+          <t>华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3630,28 +3632,32 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>郴州市新天投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK15" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK15" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
@@ -3661,17 +3667,17 @@
       </c>
       <c r="AN15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
@@ -3681,17 +3687,17 @@
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3724,74 +3730,74 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN002</t>
+          <t>26金霞01</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683460.IB</t>
+          <t>283880.SH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>28.24</v>
+        <v>37.94</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26宁沪高MTN001</t>
+          <t>25金霞01</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.78Y</t>
+          <t>4.13Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6734</t>
+          <t>1.9567</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司</t>
+          <t>湖南金霞发展集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.01</t>
+          <t>C- 10.26</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3801,7 +3807,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3815,46 +3821,44 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>5.85</v>
+      </c>
+      <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行5亿元，用于偿还发行人有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司</t>
+          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3864,79 +3868,75 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>江苏宁沪高速公路股份有限公司2026年度第二期中期票据</t>
+          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
           <t>2029-09-01</t>
         </is>
       </c>
-      <c r="AK16" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AM16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO16" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ16" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR16" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS16" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3962,108 +3962,110 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26金霞01</t>
+          <t>26高淳国资MTN001</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>283880.SH</t>
+          <t>102690020.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>37.94</v>
+        <v>59.24</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>25高淳国资MTN002</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>3.63Y+N</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>1.9715</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>--/1.8700</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>南京高淳国有资产经营控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>C- 16.69</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>08-31 09:00</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>25金霞01</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>4.13Y</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>1.9567</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>湖南金霞发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>C- 10.26</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>08-31 15:00</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="V17" s="3"/>
+        <v>5.05</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>5.38</v>
+      </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4074,23 +4076,23 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人公司债券的本金[23金霞01]</t>
+          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司,爱建证券有限责任公司</t>
+          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4100,33 +4102,37 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>湖南金霞发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK17" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4141,32 +4147,32 @@
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
@@ -4176,7 +4182,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4194,7 +4200,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26高淳国资MTN001</t>
+          <t>26宁波能源SCP002(取消发行)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4204,64 +4210,58 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102690020.IB</t>
+          <t>DY012682180.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>4.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>59.24</v>
-      </c>
+          <t>1.40 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25高淳国资MTN002</t>
+          <t>GC甬能Y1</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.63Y+N</t>
+          <t>3.51Y+N</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.9715</t>
+          <t>1.8509</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/1.8700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司</t>
+          <t>宁波能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 16.69</t>
+          <t>C- 18.20</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4284,47 +4284,47 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U18" s="4" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>5.38</v>
-      </c>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.60%~1.64%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额4亿元,资金用途为偿还发行人存量债务融资工具本金。[25高淳国资CP002]</t>
+          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司,江苏银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD18" s="3"/>
+          <t>宁波银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr">
+        <is>
+          <t>宁波开发投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>南京高淳国有资产经营控股集团有限公司2026年度第一期中期票据</t>
+          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券(取消发行)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4349,14 +4349,10 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-03-30</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -4364,7 +4360,7 @@
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
@@ -4374,7 +4370,7 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
@@ -4384,22 +4380,22 @@
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4409,12 +4405,12 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4427,27 +4423,29 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AZ18" s="3"/>
+      <c r="AZ18" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26宁波能源SCP002(取消发行)</t>
+          <t>26厦门产投MTN003(科创债)(取消发行)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>DY012682180.IB</t>
+          <t>DY102683466.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
@@ -4456,44 +4454,44 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>GC甬能Y1</t>
+          <t>26厦门产投MTN002(科创债)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>3.51Y+N</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.8509</t>
+          <t>1.9088</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8950/1.8800</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司</t>
+          <t>厦门市产业投资有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 18.20</t>
+          <t>A 75.38</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4503,7 +4501,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 11:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4513,7 +4511,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U19" s="3"/>
@@ -4525,38 +4523,38 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.64%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z19" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模5亿元,将用于偿还发行人即将到期的债务融资工具本金[25宁波能源SCP002]</t>
+          <t>本期科技创新债券发行金额为5亿元,本期发行的募集资金扣除承销费后,拟全部用于置换发行人本期科技创新债券发行之日起一年以内用于科技创新领域股权投资或基金出资的自有资金投入。</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD19" s="3" t="inlineStr">
-        <is>
-          <t>宁波开发投资集团有限公司</t>
-        </is>
-      </c>
+          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4571,7 +4569,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>宁波能源集团股份有限公司2026年度第二期超短期融资券(取消发行)</t>
+          <t>厦门市产业投资有限公司2026年度第三期科技创新债券(取消发行)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4581,149 +4579,149 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2027-03-30</t>
+          <t>2031-09-02</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AM19" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN19" s="3" t="inlineStr">
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY19" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AO19" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ19" s="3" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="AR19" s="3" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>其他电力</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX19" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY19" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AZ19" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ19" s="3"/>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN003(科创债)(取消发行)</t>
+          <t>26沪盛K1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>08-31 18:30</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>DY102683466.IB</t>
+          <t>245999.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F20" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>29.17</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN002(科创债)</t>
+          <t>26国盛MTN003(科创债)</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>9.88Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.9088</t>
+          <t>2.0875</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.8950/1.8800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司</t>
+          <t>上海国盛(集团)有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>A 75.38</t>
+          <t>C 26.09</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4733,7 +4731,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>08-31 11:00</t>
+          <t>08-31 16:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4746,16 +4744,18 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U20" s="3"/>
+      <c r="U20" s="4" t="n">
+        <v>3.93</v>
+      </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4763,30 +4763,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z20" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行金额为5亿元,本期发行的募集资金扣除承销费后,拟全部用于置换发行人本期科技创新债券发行之日起一年以内用于科技创新领域股权投资或基金出资的自有资金投入。</t>
+          <t>本期公司债券募集资金扣除发行等相关费用后，拟用于科技创新领域基金出资及置换前期支付科技创新领域股权投资的自有资金。具体募集资金用途详见“第三节  募集资金运用”。</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4796,12 +4792,12 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司2026年度第三期科技创新债券(取消发行)</t>
+          <t>上海国盛(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4811,13 +4807,13 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2036-09-02</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
@@ -4832,28 +4828,32 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP20" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="AY20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ20" s="3"/>
@@ -7212,7 +7212,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y2</t>
+          <t>26光大01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7222,64 +7222,64 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>520449.SZ</t>
+          <t>524991.SZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.0</v>
+        <v>40.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.28</v>
+        <v>1.55</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>86.94</v>
+        <v>29.24</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>24光大集团MTN004A</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.6671</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>中国光大集团股份公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 13.46</t>
+          <t>B- 37.75</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7303,45 +7303,45 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.82</v>
+        <v>3.47</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>2.02%~2.12%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z31" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD31" s="3" t="inlineStr">
-        <is>
-          <t>天府信用增进股份有限公司</t>
-        </is>
-      </c>
+          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -7359,20 +7359,24 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="AK31" s="3"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="AK31" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7390,30 +7394,34 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP31" s="3"/>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR31" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7421,12 +7429,12 @@
       </c>
       <c r="AV31" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7444,59 +7452,59 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26振兴Y3</t>
+          <t>26晋能电力GN005(碳中和债)</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>08-31 19:00</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>520450.SZ</t>
+          <t>132680093.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 3.00</t>
+          <t>1.70 ~ 2.10</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>93.94</v>
+        <v>44.96</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>25晋能电力MTN002</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>5.38Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2.1263</t>
+          <t>1.9709</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7506,12 +7514,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司</t>
+          <t>晋能控股电力集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 13.46</t>
+          <t>C+ 34.39</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7521,7 +7529,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>08-31 15:00</t>
+          <t>08-31 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7535,48 +7543,44 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>四川省-达州市</t>
+          <t>山西省-太原市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
+          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD32" s="3" t="inlineStr">
-        <is>
-          <t>成都中小企业融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7586,17 +7590,17 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
+          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
@@ -7607,58 +7611,62 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AO32" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP32" s="3"/>
-      <c r="AQ32" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7668,7 +7676,7 @@
       </c>
       <c r="AY32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AZ32" s="3"/>
@@ -7676,7 +7684,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26光大01</t>
+          <t>26振兴Y2</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7686,64 +7694,64 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>524991.SZ</t>
+          <t>520449.SZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>40.0</v>
+        <v>3.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.55</v>
+        <v>2.28</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>29.24</v>
+        <v>86.94</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>24光大集团MTN004A</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.6671</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B- 37.75</t>
+          <t>C- 13.46</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7767,45 +7775,45 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.47</v>
+        <v>3.82</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.02%~2.12%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期发行的公司债券募集资金扣除发行等相关费用后,全部用于补充营运资金;本期债券募集资金补充日常生产经营所需流动资金,将根据公司财务状况和资金使用需求,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>天府信用增进股份有限公司</t>
+        </is>
+      </c>
       <c r="AE33" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7813,7 +7821,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -7823,24 +7831,20 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>中国光大集团股份公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="AK33" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7858,32 +7862,28 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP33" s="3"/>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7916,59 +7916,59 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26晋能电力GN005(碳中和债)</t>
+          <t>26振兴Y3</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>08-31 19:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>132680093.IB</t>
+          <t>520450.SZ</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
+          <t>1.90 ~ 3.00</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>44.96</v>
+        <v>93.94</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25晋能电力MTN002</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>5.38Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.9709</t>
+          <t>2.1263</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司</t>
+          <t>达州市振兴科技发展有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.39</t>
+          <t>C- 13.46</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>08-31 09:00</t>
+          <t>08-31 15:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -8007,44 +8007,48 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.24</v>
+        <v>2.88</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>2.17%~2.27%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>山西省-太原市</t>
+          <t>四川省-达州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0亿元，发行上限金额人民币5亿元，拟用于偿还“晋能控股电力集团有限公司2023年度第十一期绿色中期票据(碳中和债)(债券简称：23晋能电力GN011(碳中和债))”。[23晋能电力GN011(碳中和债)]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人及其子公司的有息负债</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3"/>
+          <t>平安证券股份有限公司,华鑫证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr">
+        <is>
+          <t>成都中小企业融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8054,17 +8058,17 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司2026年度第五期绿色中期票据(碳中和债)</t>
+          <t>达州市振兴科技发展有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种三)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
@@ -8075,7 +8079,7 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -8093,29 +8097,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP34" s="3"/>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX34" s="3" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="AY34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AZ34" s="3"/>
